--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_real_estate_operations_services.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2000956309241895</v>
+        <v>0.1997928183516184</v>
       </c>
       <c r="C2">
-        <v>26.20283417512568</v>
+        <v>25.99196355554482</v>
       </c>
       <c r="D2">
-        <v>25.78783417512568</v>
+        <v>25.83854355554482</v>
       </c>
       <c r="E2">
-        <v>-0.058</v>
+        <v>0.20358</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.26158</v>
       </c>
       <c r="G2">
         <v>0.415</v>
@@ -1579,28 +1579,28 @@
         <v>0.242</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.013157474</v>
       </c>
       <c r="N2">
-        <v>0.242</v>
+        <v>0.228842526</v>
       </c>
       <c r="O2">
-        <v>0.04114</v>
+        <v>0.03890322942</v>
       </c>
       <c r="P2">
-        <v>0.20086</v>
+        <v>0.18993929658</v>
       </c>
       <c r="Q2">
-        <v>0.31786</v>
+        <v>0.30693929658</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2000956309241895</v>
+        <v>0.2013892205571903</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.5572147686649918</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>18.39258812139777</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1997928183516184</v>
+        <v>0.1995431257790473</v>
       </c>
       <c r="C3">
-        <v>25.99196355554482</v>
+        <v>25.77234765884494</v>
       </c>
       <c r="D3">
-        <v>25.83854355554482</v>
+        <v>25.88050765884494</v>
       </c>
       <c r="E3">
-        <v>0.20358</v>
+        <v>0.4651600000000001</v>
       </c>
       <c r="F3">
-        <v>0.26158</v>
+        <v>0.5231600000000001</v>
       </c>
       <c r="G3">
         <v>0.415</v>
@@ -1661,45 +1661,45 @@
         <v>0.242</v>
       </c>
       <c r="M3">
-        <v>0.013157474</v>
+        <v>0.02798906</v>
       </c>
       <c r="N3">
-        <v>0.228842526</v>
+        <v>0.21401094</v>
       </c>
       <c r="O3">
-        <v>0.03890322942</v>
+        <v>0.0363818598</v>
       </c>
       <c r="P3">
-        <v>0.18993929658</v>
+        <v>0.1776290802</v>
       </c>
       <c r="Q3">
-        <v>0.30693929658</v>
+        <v>0.2946290802</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2013892205571903</v>
+        <v>0.2027092099786197</v>
       </c>
       <c r="T3">
-        <v>0.5572147686649918</v>
+        <v>0.5619420730210904</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V3">
         <v>0.17</v>
       </c>
       <c r="W3">
-        <v>0.04174899999999999</v>
+        <v>0.044405</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y3">
-        <v>18.39258812139777</v>
+        <v>8.64623535052624</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1995431257790473</v>
+        <v>0.1993116932064762</v>
       </c>
       <c r="C4">
-        <v>25.77234765884494</v>
+        <v>25.54978483298865</v>
       </c>
       <c r="D4">
-        <v>25.88050765884494</v>
+        <v>25.91952483298865</v>
       </c>
       <c r="E4">
-        <v>0.4651600000000001</v>
+        <v>0.7267399999999999</v>
       </c>
       <c r="F4">
-        <v>0.5231600000000001</v>
+        <v>0.78474</v>
       </c>
       <c r="G4">
         <v>0.415</v>
@@ -1743,45 +1743,45 @@
         <v>0.242</v>
       </c>
       <c r="M4">
-        <v>0.02798906</v>
+        <v>0.043396122</v>
       </c>
       <c r="N4">
-        <v>0.21401094</v>
+        <v>0.198603878</v>
       </c>
       <c r="O4">
-        <v>0.0363818598</v>
+        <v>0.03376265926</v>
       </c>
       <c r="P4">
-        <v>0.1776290802</v>
+        <v>0.16484121874</v>
       </c>
       <c r="Q4">
-        <v>0.2946290802</v>
+        <v>0.28184121874</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2027092099786197</v>
+        <v>0.2040564156767795</v>
       </c>
       <c r="T4">
-        <v>0.5619420730210904</v>
+        <v>0.5667668475700983</v>
       </c>
       <c r="U4">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V4">
         <v>0.17</v>
       </c>
       <c r="W4">
-        <v>0.044405</v>
+        <v>0.045899</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y4">
-        <v>8.64623535052624</v>
+        <v>5.576535156758937</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1993116932064762</v>
+        <v>0.199133380633905</v>
       </c>
       <c r="C5">
-        <v>25.54978483298865</v>
+        <v>25.31834684859989</v>
       </c>
       <c r="D5">
-        <v>25.91952483298865</v>
+        <v>25.94966684859989</v>
       </c>
       <c r="E5">
-        <v>0.7267399999999999</v>
+        <v>0.9883200000000001</v>
       </c>
       <c r="F5">
-        <v>0.78474</v>
+        <v>1.04632</v>
       </c>
       <c r="G5">
         <v>0.415</v>
@@ -1825,45 +1825,45 @@
         <v>0.242</v>
       </c>
       <c r="M5">
-        <v>0.043396122</v>
+        <v>0.06047729600000001</v>
       </c>
       <c r="N5">
-        <v>0.198603878</v>
+        <v>0.181522704</v>
       </c>
       <c r="O5">
-        <v>0.03376265926</v>
+        <v>0.03085885968</v>
       </c>
       <c r="P5">
-        <v>0.16484121874</v>
+        <v>0.15066384432</v>
       </c>
       <c r="Q5">
-        <v>0.28184121874</v>
+        <v>0.26766384432</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2040564156767795</v>
+        <v>0.2054316881603178</v>
       </c>
       <c r="T5">
-        <v>0.5667668475700983</v>
+        <v>0.571692138255544</v>
       </c>
       <c r="U5">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V5">
         <v>0.17</v>
       </c>
       <c r="W5">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y5">
-        <v>5.576535156758937</v>
+        <v>4.001501654439046</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.199133380633905</v>
+        <v>0.1994779680613339</v>
       </c>
       <c r="C6">
-        <v>25.31834684859989</v>
+        <v>24.99858070093801</v>
       </c>
       <c r="D6">
-        <v>25.94966684859989</v>
+        <v>25.89148070093801</v>
       </c>
       <c r="E6">
-        <v>0.9883200000000001</v>
+        <v>1.2499</v>
       </c>
       <c r="F6">
-        <v>1.04632</v>
+        <v>1.3079</v>
       </c>
       <c r="G6">
         <v>0.415</v>
@@ -1907,45 +1907,45 @@
         <v>0.242</v>
       </c>
       <c r="M6">
-        <v>0.06047729600000001</v>
+        <v>0.09403801000000001</v>
       </c>
       <c r="N6">
-        <v>0.181522704</v>
+        <v>0.14796199</v>
       </c>
       <c r="O6">
-        <v>0.03085885968</v>
+        <v>0.0251535383</v>
       </c>
       <c r="P6">
-        <v>0.15066384432</v>
+        <v>0.1228084517</v>
       </c>
       <c r="Q6">
-        <v>0.26766384432</v>
+        <v>0.2398084517</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2054316881603178</v>
+        <v>0.2068359137487725</v>
       </c>
       <c r="T6">
-        <v>0.571692138255544</v>
+        <v>0.5767211192712094</v>
       </c>
       <c r="U6">
-        <v>0.0578</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V6">
         <v>0.17</v>
       </c>
       <c r="W6">
-        <v>0.047974</v>
+        <v>0.059677</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>4.001501654439046</v>
+        <v>2.573427489586392</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1994779680613339</v>
+        <v>0.1995486554887628</v>
       </c>
       <c r="C7">
-        <v>24.99858070093801</v>
+        <v>24.72509684293511</v>
       </c>
       <c r="D7">
-        <v>25.89148070093801</v>
+        <v>25.87957684293511</v>
       </c>
       <c r="E7">
-        <v>1.2499</v>
+        <v>1.51148</v>
       </c>
       <c r="F7">
-        <v>1.3079</v>
+        <v>1.56948</v>
       </c>
       <c r="G7">
         <v>0.415</v>
@@ -1989,45 +1989,45 @@
         <v>0.242</v>
       </c>
       <c r="M7">
-        <v>0.09403801000000001</v>
+        <v>0.118966584</v>
       </c>
       <c r="N7">
-        <v>0.14796199</v>
+        <v>0.123033416</v>
       </c>
       <c r="O7">
-        <v>0.0251535383</v>
+        <v>0.02091568072</v>
       </c>
       <c r="P7">
-        <v>0.1228084517</v>
+        <v>0.10211773528</v>
       </c>
       <c r="Q7">
-        <v>0.2398084517</v>
+        <v>0.2191177352799999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2068359137487725</v>
+        <v>0.2082700164774072</v>
       </c>
       <c r="T7">
-        <v>0.5767211192712094</v>
+        <v>0.5818570998829529</v>
       </c>
       <c r="U7">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V7">
         <v>0.17</v>
       </c>
       <c r="W7">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y7">
-        <v>2.573427489586392</v>
+        <v>2.034184658105338</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1995486554887628</v>
+        <v>0.2039398256323325</v>
       </c>
       <c r="C8">
-        <v>24.72509684293511</v>
+        <v>23.74490200504395</v>
       </c>
       <c r="D8">
-        <v>25.87957684293511</v>
+        <v>25.16096200504395</v>
       </c>
       <c r="E8">
-        <v>1.51148</v>
+        <v>1.77306</v>
       </c>
       <c r="F8">
-        <v>1.56948</v>
+        <v>1.83106</v>
       </c>
       <c r="G8">
         <v>0.415</v>
@@ -2071,45 +2071,45 @@
         <v>0.242</v>
       </c>
       <c r="M8">
-        <v>0.118966584</v>
+        <v>0.268799608</v>
       </c>
       <c r="N8">
-        <v>0.123033416</v>
+        <v>-0.02679960800000003</v>
       </c>
       <c r="O8">
-        <v>0.02091568072</v>
+        <v>-0.004555933360000005</v>
       </c>
       <c r="P8">
-        <v>0.10211773528</v>
+        <v>-0.02224367464000002</v>
       </c>
       <c r="Q8">
-        <v>0.21911773528</v>
+        <v>0.09475632535999998</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2082700164774072</v>
+        <v>0.2099318019812831</v>
       </c>
       <c r="T8">
-        <v>0.5818570998829529</v>
+        <v>0.587808485343957</v>
       </c>
       <c r="U8">
-        <v>0.07580000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V8">
-        <v>0.17</v>
+        <v>0.1530508184372054</v>
       </c>
       <c r="W8">
-        <v>0.062914</v>
+        <v>0.1243321398534182</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.034184658105338</v>
+        <v>0.9002989319835615</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2039398256323325</v>
+        <v>0.2097143723176224</v>
       </c>
       <c r="C9">
-        <v>23.74490200504395</v>
+        <v>22.59692535970652</v>
       </c>
       <c r="D9">
-        <v>25.16096200504395</v>
+        <v>24.27456535970652</v>
       </c>
       <c r="E9">
-        <v>1.77306</v>
+        <v>2.03464</v>
       </c>
       <c r="F9">
-        <v>1.83106</v>
+        <v>2.09264</v>
       </c>
       <c r="G9">
         <v>0.415</v>
@@ -2153,45 +2153,45 @@
         <v>0.242</v>
       </c>
       <c r="M9">
-        <v>0.2687996080000001</v>
+        <v>0.4202021120000001</v>
       </c>
       <c r="N9">
-        <v>-0.02679960800000009</v>
+        <v>-0.1782021120000001</v>
       </c>
       <c r="O9">
-        <v>-0.004555933360000015</v>
+        <v>-0.03029435904000002</v>
       </c>
       <c r="P9">
-        <v>-0.02224367464000007</v>
+        <v>-0.1479077529600001</v>
       </c>
       <c r="Q9">
-        <v>0.09475632535999992</v>
+        <v>-0.03090775296000006</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2099318019812831</v>
+        <v>0.2121990462259599</v>
       </c>
       <c r="T9">
-        <v>0.587808485343957</v>
+        <v>0.5959282122297939</v>
       </c>
       <c r="U9">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V9">
-        <v>0.1530508184372054</v>
+        <v>0.09790526707300318</v>
       </c>
       <c r="W9">
-        <v>0.1243321398534182</v>
+        <v>0.181140622371741</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y9">
-        <v>0.9002989319835613</v>
+        <v>0.5759133357235481</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2097143723176224</v>
+        <v>0.2112643723176224</v>
       </c>
       <c r="C10">
-        <v>22.59692535970652</v>
+        <v>22.10795153600579</v>
       </c>
       <c r="D10">
-        <v>24.27456535970652</v>
+        <v>24.04717153600579</v>
       </c>
       <c r="E10">
-        <v>2.03464</v>
+        <v>2.29622</v>
       </c>
       <c r="F10">
-        <v>2.09264</v>
+        <v>2.35422</v>
       </c>
       <c r="G10">
         <v>0.415</v>
@@ -2235,37 +2235,37 @@
         <v>0.242</v>
       </c>
       <c r="M10">
-        <v>0.4202021120000001</v>
+        <v>0.472727376</v>
       </c>
       <c r="N10">
-        <v>-0.1782021120000001</v>
+        <v>-0.230727376</v>
       </c>
       <c r="O10">
-        <v>-0.03029435904000002</v>
+        <v>-0.03922365392000001</v>
       </c>
       <c r="P10">
-        <v>-0.1479077529600001</v>
+        <v>-0.19150372208</v>
       </c>
       <c r="Q10">
-        <v>-0.03090775296000006</v>
+        <v>-0.07450372208000003</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2121990462259599</v>
+        <v>0.2140276071734979</v>
       </c>
       <c r="T10">
-        <v>0.5959282122297939</v>
+        <v>0.6024768739026488</v>
       </c>
       <c r="U10">
         <v>0.2008</v>
       </c>
       <c r="V10">
-        <v>0.09790526707300318</v>
+        <v>0.08702690406489173</v>
       </c>
       <c r="W10">
-        <v>0.181140622371741</v>
+        <v>0.1833249976637698</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.5759133357235481</v>
+        <v>0.5119229650875983</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2112643723176224</v>
+        <v>0.2164937522746653</v>
       </c>
       <c r="C11">
-        <v>22.10795153600579</v>
+        <v>21.1096615206819</v>
       </c>
       <c r="D11">
-        <v>24.04717153600579</v>
+        <v>23.3104615206819</v>
       </c>
       <c r="E11">
-        <v>2.29622</v>
+        <v>2.5578</v>
       </c>
       <c r="F11">
-        <v>2.35422</v>
+        <v>2.6158</v>
       </c>
       <c r="G11">
         <v>0.415</v>
@@ -2317,45 +2317,45 @@
         <v>0.242</v>
       </c>
       <c r="M11">
-        <v>0.472727376</v>
+        <v>0.61680564</v>
       </c>
       <c r="N11">
-        <v>-0.230727376</v>
+        <v>-0.3748056400000001</v>
       </c>
       <c r="O11">
-        <v>-0.03922365392000001</v>
+        <v>-0.06371695880000001</v>
       </c>
       <c r="P11">
-        <v>-0.19150372208</v>
+        <v>-0.3110886812000001</v>
       </c>
       <c r="Q11">
-        <v>-0.07450372208000003</v>
+        <v>-0.1940886812000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2140276071734979</v>
+        <v>0.2160961138721401</v>
       </c>
       <c r="T11">
-        <v>0.6024768739026488</v>
+        <v>0.6098848580640078</v>
       </c>
       <c r="U11">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.08702690406489173</v>
+        <v>0.06669848219935212</v>
       </c>
       <c r="W11">
-        <v>0.1833249976637698</v>
+        <v>0.2200724978973928</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.5119229650875983</v>
+        <v>0.3923440129373654</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2164937522746653</v>
+        <v>0.2183937522746653</v>
       </c>
       <c r="C12">
-        <v>21.1096615206819</v>
+        <v>20.59146807838989</v>
       </c>
       <c r="D12">
-        <v>23.3104615206819</v>
+        <v>23.05384807838989</v>
       </c>
       <c r="E12">
-        <v>2.5578</v>
+        <v>2.81938</v>
       </c>
       <c r="F12">
-        <v>2.6158</v>
+        <v>2.87738</v>
       </c>
       <c r="G12">
         <v>0.415</v>
@@ -2399,37 +2399,37 @@
         <v>0.242</v>
       </c>
       <c r="M12">
-        <v>0.61680564</v>
+        <v>0.678486204</v>
       </c>
       <c r="N12">
-        <v>-0.3748056400000001</v>
+        <v>-0.436486204</v>
       </c>
       <c r="O12">
-        <v>-0.06371695880000001</v>
+        <v>-0.07420265468000001</v>
       </c>
       <c r="P12">
-        <v>-0.3110886812000001</v>
+        <v>-0.3622835493200001</v>
       </c>
       <c r="Q12">
-        <v>-0.1940886812000001</v>
+        <v>-0.2452835493200001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2160961138721401</v>
+        <v>0.2180095533538495</v>
       </c>
       <c r="T12">
-        <v>0.6098848580640078</v>
+        <v>0.6167374969186595</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.06669848219935212</v>
+        <v>0.06063498381759284</v>
       </c>
       <c r="W12">
-        <v>0.2200724978973928</v>
+        <v>0.2215022708158116</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.3923440129373654</v>
+        <v>0.356676375397605</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2183937522746653</v>
+        <v>0.2202937522746653</v>
       </c>
       <c r="C13">
-        <v>20.59146807838989</v>
+        <v>20.07886297990961</v>
       </c>
       <c r="D13">
-        <v>23.05384807838989</v>
+        <v>22.80282297990961</v>
       </c>
       <c r="E13">
-        <v>2.81938</v>
+        <v>3.08096</v>
       </c>
       <c r="F13">
-        <v>2.87738</v>
+        <v>3.13896</v>
       </c>
       <c r="G13">
         <v>0.415</v>
@@ -2481,37 +2481,37 @@
         <v>0.242</v>
       </c>
       <c r="M13">
-        <v>0.678486204</v>
+        <v>0.740166768</v>
       </c>
       <c r="N13">
-        <v>-0.436486204</v>
+        <v>-0.498166768</v>
       </c>
       <c r="O13">
-        <v>-0.07420265468000001</v>
+        <v>-0.08468835056000001</v>
       </c>
       <c r="P13">
-        <v>-0.3622835493200001</v>
+        <v>-0.41347841744</v>
       </c>
       <c r="Q13">
-        <v>-0.2452835493200001</v>
+        <v>-0.29647841744</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2180095533538495</v>
+        <v>0.2199664800965069</v>
       </c>
       <c r="T13">
-        <v>0.6167374969186595</v>
+        <v>0.6237458775654625</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.06063498381759284</v>
+        <v>0.05558206849946012</v>
       </c>
       <c r="W13">
-        <v>0.2215022708158116</v>
+        <v>0.2226937482478273</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.356676375397605</v>
+        <v>0.3269533441144712</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2202937522746653</v>
+        <v>0.2221937522746653</v>
       </c>
       <c r="C14">
-        <v>20.07886297990961</v>
+        <v>19.57166564310981</v>
       </c>
       <c r="D14">
-        <v>22.80282297990961</v>
+        <v>22.55720564310981</v>
       </c>
       <c r="E14">
-        <v>3.08096</v>
+        <v>3.342540000000001</v>
       </c>
       <c r="F14">
-        <v>3.13896</v>
+        <v>3.40054</v>
       </c>
       <c r="G14">
         <v>0.415</v>
@@ -2563,37 +2563,37 @@
         <v>0.242</v>
       </c>
       <c r="M14">
-        <v>0.740166768</v>
+        <v>0.8018473320000001</v>
       </c>
       <c r="N14">
-        <v>-0.498166768</v>
+        <v>-0.5598473320000001</v>
       </c>
       <c r="O14">
-        <v>-0.08468835056000001</v>
+        <v>-0.09517404644000003</v>
       </c>
       <c r="P14">
-        <v>-0.41347841744</v>
+        <v>-0.4646732855600001</v>
       </c>
       <c r="Q14">
-        <v>-0.29647841744</v>
+        <v>-0.3476732855600001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2199664800965069</v>
+        <v>0.2219683936608345</v>
       </c>
       <c r="T14">
-        <v>0.6237458775654625</v>
+        <v>0.6309153704110425</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.05558206849946012</v>
+        <v>0.0513065247687324</v>
       </c>
       <c r="W14">
-        <v>0.2226937482478273</v>
+        <v>0.2237019214595329</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3269533441144712</v>
+        <v>0.3018030868748964</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2221937522746653</v>
+        <v>0.2240937522746654</v>
       </c>
       <c r="C15">
-        <v>19.57166564310981</v>
+        <v>19.06970318340429</v>
       </c>
       <c r="D15">
-        <v>22.55720564310981</v>
+        <v>22.3168231834043</v>
       </c>
       <c r="E15">
-        <v>3.342540000000001</v>
+        <v>3.604120000000001</v>
       </c>
       <c r="F15">
-        <v>3.40054</v>
+        <v>3.662120000000001</v>
       </c>
       <c r="G15">
         <v>0.415</v>
@@ -2645,37 +2645,37 @@
         <v>0.242</v>
       </c>
       <c r="M15">
-        <v>0.8018473320000001</v>
+        <v>0.8635278960000002</v>
       </c>
       <c r="N15">
-        <v>-0.5598473320000001</v>
+        <v>-0.6215278960000002</v>
       </c>
       <c r="O15">
-        <v>-0.09517404644000003</v>
+        <v>-0.1056597423200001</v>
       </c>
       <c r="P15">
-        <v>-0.4646732855600001</v>
+        <v>-0.5158681536800002</v>
       </c>
       <c r="Q15">
-        <v>-0.3476732855600001</v>
+        <v>-0.3988681536800002</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2219683936608345</v>
+        <v>0.2240168633545652</v>
       </c>
       <c r="T15">
-        <v>0.6309153704110425</v>
+        <v>0.6382515956483803</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.0513065247687324</v>
+        <v>0.04764177299953722</v>
       </c>
       <c r="W15">
-        <v>0.2237019214595329</v>
+        <v>0.2245660699267091</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3018030868748964</v>
+        <v>0.2802457235266895</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2240937522746654</v>
+        <v>0.2259937522746653</v>
       </c>
       <c r="C16">
-        <v>19.06970318340429</v>
+        <v>18.57281000792952</v>
       </c>
       <c r="D16">
-        <v>22.3168231834043</v>
+        <v>22.08151000792952</v>
       </c>
       <c r="E16">
-        <v>3.604120000000001</v>
+        <v>3.865700000000001</v>
       </c>
       <c r="F16">
-        <v>3.662120000000001</v>
+        <v>3.923700000000001</v>
       </c>
       <c r="G16">
         <v>0.415</v>
@@ -2727,37 +2727,37 @@
         <v>0.242</v>
       </c>
       <c r="M16">
-        <v>0.8635278960000002</v>
+        <v>0.9252084600000002</v>
       </c>
       <c r="N16">
-        <v>-0.6215278960000002</v>
+        <v>-0.6832084600000002</v>
       </c>
       <c r="O16">
-        <v>-0.1056597423200001</v>
+        <v>-0.1161454382</v>
       </c>
       <c r="P16">
-        <v>-0.5158681536800002</v>
+        <v>-0.5670630218000002</v>
       </c>
       <c r="Q16">
-        <v>-0.3988681536800002</v>
+        <v>-0.4500630218000002</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2240168633545652</v>
+        <v>0.2261135323352071</v>
       </c>
       <c r="T16">
-        <v>0.6382515956483803</v>
+        <v>0.6457604379501259</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.04764177299953722</v>
+        <v>0.04446565479956808</v>
       </c>
       <c r="W16">
-        <v>0.2245660699267091</v>
+        <v>0.2253149985982618</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.2802457235266895</v>
+        <v>0.261562675291577</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2259937522746653</v>
+        <v>0.2278937522746653</v>
       </c>
       <c r="C17">
-        <v>18.57281000792952</v>
+        <v>18.08082743512854</v>
       </c>
       <c r="D17">
-        <v>22.08151000792952</v>
+        <v>21.85110743512854</v>
       </c>
       <c r="E17">
-        <v>3.8657</v>
+        <v>4.127280000000001</v>
       </c>
       <c r="F17">
-        <v>3.9237</v>
+        <v>4.185280000000001</v>
       </c>
       <c r="G17">
         <v>0.415</v>
@@ -2809,37 +2809,37 @@
         <v>0.242</v>
       </c>
       <c r="M17">
-        <v>0.9252084600000001</v>
+        <v>0.9868890240000002</v>
       </c>
       <c r="N17">
-        <v>-0.6832084600000001</v>
+        <v>-0.7448890240000002</v>
       </c>
       <c r="O17">
-        <v>-0.1161454382</v>
+        <v>-0.12663113408</v>
       </c>
       <c r="P17">
-        <v>-0.5670630218000001</v>
+        <v>-0.6182578899200002</v>
       </c>
       <c r="Q17">
-        <v>-0.4500630218000001</v>
+        <v>-0.5012578899200002</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2261135323352071</v>
+        <v>0.2282601220058643</v>
       </c>
       <c r="T17">
-        <v>0.6457604379501259</v>
+        <v>0.6534480622114369</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.04446565479956809</v>
+        <v>0.04168655137459507</v>
       </c>
       <c r="W17">
-        <v>0.2253149985982618</v>
+        <v>0.2259703111858705</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.261562675291577</v>
+        <v>0.2452150080858534</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2278937522746653</v>
+        <v>0.2297937522746653</v>
       </c>
       <c r="C18">
-        <v>18.08082743512854</v>
+        <v>17.59360333790524</v>
       </c>
       <c r="D18">
-        <v>21.85110743512854</v>
+        <v>21.62546333790524</v>
       </c>
       <c r="E18">
-        <v>4.127280000000001</v>
+        <v>4.388860000000001</v>
       </c>
       <c r="F18">
-        <v>4.185280000000001</v>
+        <v>4.446860000000001</v>
       </c>
       <c r="G18">
         <v>0.415</v>
@@ -2891,37 +2891,37 @@
         <v>0.242</v>
       </c>
       <c r="M18">
-        <v>0.9868890240000002</v>
+        <v>1.048569588</v>
       </c>
       <c r="N18">
-        <v>-0.7448890240000002</v>
+        <v>-0.8065695880000003</v>
       </c>
       <c r="O18">
-        <v>-0.12663113408</v>
+        <v>-0.1371168299600001</v>
       </c>
       <c r="P18">
-        <v>-0.6182578899200002</v>
+        <v>-0.6694527580400003</v>
       </c>
       <c r="Q18">
-        <v>-0.5012578899200002</v>
+        <v>-0.5524527580400003</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2282601220058643</v>
+        <v>0.2304584367288265</v>
       </c>
       <c r="T18">
-        <v>0.6534480622114369</v>
+        <v>0.6613209304308517</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.04168655137459507</v>
+        <v>0.03923440129373654</v>
       </c>
       <c r="W18">
-        <v>0.2259703111858705</v>
+        <v>0.2265485281749369</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2452150080858534</v>
+        <v>0.230790595845509</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2297937522746653</v>
+        <v>0.2316937522746653</v>
       </c>
       <c r="C19">
-        <v>17.59360333790524</v>
+        <v>17.11099180866207</v>
       </c>
       <c r="D19">
-        <v>21.62546333790524</v>
+        <v>21.40443180866207</v>
       </c>
       <c r="E19">
-        <v>4.388860000000001</v>
+        <v>4.650440000000001</v>
       </c>
       <c r="F19">
-        <v>4.446860000000001</v>
+        <v>4.70844</v>
       </c>
       <c r="G19">
         <v>0.415</v>
@@ -2973,37 +2973,37 @@
         <v>0.242</v>
       </c>
       <c r="M19">
-        <v>1.048569588</v>
+        <v>1.110250152</v>
       </c>
       <c r="N19">
-        <v>-0.8065695880000003</v>
+        <v>-0.8682501520000001</v>
       </c>
       <c r="O19">
-        <v>-0.1371168299600001</v>
+        <v>-0.14760252584</v>
       </c>
       <c r="P19">
-        <v>-0.6694527580400003</v>
+        <v>-0.7206476261600001</v>
       </c>
       <c r="Q19">
-        <v>-0.5524527580400003</v>
+        <v>-0.6036476261600001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2304584367288265</v>
+        <v>0.2327103688840562</v>
       </c>
       <c r="T19">
-        <v>0.6613209304308517</v>
+        <v>0.66938581982635</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.03923440129373654</v>
+        <v>0.03705471233297341</v>
       </c>
       <c r="W19">
-        <v>0.2265485281749369</v>
+        <v>0.2270624988318849</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.230790595845509</v>
+        <v>0.2179688960763141</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2316937522746653</v>
+        <v>0.2335937522746653</v>
       </c>
       <c r="C20">
-        <v>17.11099180866207</v>
+        <v>16.63285284467175</v>
       </c>
       <c r="D20">
-        <v>21.40443180866207</v>
+        <v>21.18787284467174</v>
       </c>
       <c r="E20">
-        <v>4.650440000000001</v>
+        <v>4.91202</v>
       </c>
       <c r="F20">
-        <v>4.70844</v>
+        <v>4.97002</v>
       </c>
       <c r="G20">
         <v>0.415</v>
@@ -3055,37 +3055,37 @@
         <v>0.242</v>
       </c>
       <c r="M20">
-        <v>1.110250152</v>
+        <v>1.171930716</v>
       </c>
       <c r="N20">
-        <v>-0.8682501520000001</v>
+        <v>-0.9299307160000001</v>
       </c>
       <c r="O20">
-        <v>-0.14760252584</v>
+        <v>-0.15808822172</v>
       </c>
       <c r="P20">
-        <v>-0.7206476261600001</v>
+        <v>-0.7718424942800001</v>
       </c>
       <c r="Q20">
-        <v>-0.6036476261600001</v>
+        <v>-0.6548424942800001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2327103688840562</v>
+        <v>0.2350179043023778</v>
       </c>
       <c r="T20">
-        <v>0.66938581982635</v>
+        <v>0.677649842293342</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.03705471233297341</v>
+        <v>0.03510446431544849</v>
       </c>
       <c r="W20">
-        <v>0.2270624988318849</v>
+        <v>0.2275223673144173</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2179688960763141</v>
+        <v>0.2064968489144029</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2335937522746653</v>
+        <v>0.2354937522746653</v>
       </c>
       <c r="C21">
-        <v>16.63285284467175</v>
+        <v>16.15905205235705</v>
       </c>
       <c r="D21">
-        <v>21.18787284467174</v>
+        <v>20.97565205235706</v>
       </c>
       <c r="E21">
-        <v>4.91202</v>
+        <v>5.1736</v>
       </c>
       <c r="F21">
-        <v>4.97002</v>
+        <v>5.2316</v>
       </c>
       <c r="G21">
         <v>0.415</v>
@@ -3137,37 +3137,37 @@
         <v>0.242</v>
       </c>
       <c r="M21">
-        <v>1.171930716</v>
+        <v>1.23361128</v>
       </c>
       <c r="N21">
-        <v>-0.9299307160000001</v>
+        <v>-0.9916112800000001</v>
       </c>
       <c r="O21">
-        <v>-0.15808822172</v>
+        <v>-0.1685739176</v>
       </c>
       <c r="P21">
-        <v>-0.7718424942800001</v>
+        <v>-0.8230373624</v>
       </c>
       <c r="Q21">
-        <v>-0.6548424942800001</v>
+        <v>-0.7060373624</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2350179043023778</v>
+        <v>0.2373831281061575</v>
       </c>
       <c r="T21">
-        <v>0.677649842293342</v>
+        <v>0.6861204653220087</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.03510446431544849</v>
+        <v>0.03334924109967606</v>
       </c>
       <c r="W21">
-        <v>0.2275223673144173</v>
+        <v>0.2279362489486964</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2064968489144029</v>
+        <v>0.1961720064686827</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2354937522746653</v>
+        <v>0.2373937522746654</v>
       </c>
       <c r="C22">
-        <v>16.15905205235705</v>
+        <v>15.68946036916633</v>
       </c>
       <c r="D22">
-        <v>20.97565205235706</v>
+        <v>20.76764036916633</v>
       </c>
       <c r="E22">
-        <v>5.1736</v>
+        <v>5.435180000000001</v>
       </c>
       <c r="F22">
-        <v>5.2316</v>
+        <v>5.493180000000001</v>
       </c>
       <c r="G22">
         <v>0.415</v>
@@ -3219,37 +3219,37 @@
         <v>0.242</v>
       </c>
       <c r="M22">
-        <v>1.23361128</v>
+        <v>1.295291844</v>
       </c>
       <c r="N22">
-        <v>-0.9916112800000001</v>
+        <v>-1.053291844</v>
       </c>
       <c r="O22">
-        <v>-0.1685739176</v>
+        <v>-0.1790596134800001</v>
       </c>
       <c r="P22">
-        <v>-0.8230373624</v>
+        <v>-0.8742322305200002</v>
       </c>
       <c r="Q22">
-        <v>-0.7060373624</v>
+        <v>-0.7572322305200002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2373831281061575</v>
+        <v>0.2398082309935773</v>
       </c>
       <c r="T22">
-        <v>0.6861204653220087</v>
+        <v>0.6948055345033001</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.03334924109967606</v>
+        <v>0.03176118199969148</v>
       </c>
       <c r="W22">
-        <v>0.2279362489486964</v>
+        <v>0.2283107132844727</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1961720064686827</v>
+        <v>0.1868304823511264</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2373937522746653</v>
+        <v>0.2392937522746654</v>
       </c>
       <c r="C23">
-        <v>15.68946036916634</v>
+        <v>15.22395380183508</v>
       </c>
       <c r="D23">
-        <v>20.76764036916634</v>
+        <v>20.56371380183508</v>
       </c>
       <c r="E23">
-        <v>5.43518</v>
+        <v>5.69676</v>
       </c>
       <c r="F23">
-        <v>5.49318</v>
+        <v>5.75476</v>
       </c>
       <c r="G23">
         <v>0.415</v>
@@ -3301,37 +3301,37 @@
         <v>0.242</v>
       </c>
       <c r="M23">
-        <v>1.295291844</v>
+        <v>1.356972408</v>
       </c>
       <c r="N23">
-        <v>-1.053291844</v>
+        <v>-1.114972408</v>
       </c>
       <c r="O23">
-        <v>-0.17905961348</v>
+        <v>-0.18954530936</v>
       </c>
       <c r="P23">
-        <v>-0.8742322305200001</v>
+        <v>-0.9254270986400001</v>
       </c>
       <c r="Q23">
-        <v>-0.7572322305200001</v>
+        <v>-0.8084270986400001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2398082309935773</v>
+        <v>0.2422955160063155</v>
       </c>
       <c r="T23">
-        <v>0.6948055345033001</v>
+        <v>0.7037132977661629</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.03176118199969149</v>
+        <v>0.03031749190879642</v>
       </c>
       <c r="W23">
-        <v>0.2283107132844727</v>
+        <v>0.2286511354079058</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1868304823511264</v>
+        <v>0.1783381876988025</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2392937522746654</v>
+        <v>0.2411937522746653</v>
       </c>
       <c r="C24">
-        <v>15.22395380183508</v>
+        <v>14.76241317991835</v>
       </c>
       <c r="D24">
-        <v>20.56371380183508</v>
+        <v>20.36375317991835</v>
       </c>
       <c r="E24">
-        <v>5.69676</v>
+        <v>5.958340000000001</v>
       </c>
       <c r="F24">
-        <v>5.75476</v>
+        <v>6.01634</v>
       </c>
       <c r="G24">
         <v>0.415</v>
@@ -3383,37 +3383,37 @@
         <v>0.242</v>
       </c>
       <c r="M24">
-        <v>1.356972408</v>
+        <v>1.418652972</v>
       </c>
       <c r="N24">
-        <v>-1.114972408</v>
+        <v>-1.176652972</v>
       </c>
       <c r="O24">
-        <v>-0.18954530936</v>
+        <v>-0.20003100524</v>
       </c>
       <c r="P24">
-        <v>-0.9254270986400001</v>
+        <v>-0.97662196676</v>
       </c>
       <c r="Q24">
-        <v>-0.8084270986400001</v>
+        <v>-0.85962196676</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2422955160063155</v>
+        <v>0.2448474058245793</v>
       </c>
       <c r="T24">
-        <v>0.7037132977661629</v>
+        <v>0.7128524315033857</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.03031749190879642</v>
+        <v>0.02899934008667484</v>
       </c>
       <c r="W24">
-        <v>0.2286511354079058</v>
+        <v>0.2289619556075621</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1783381876988025</v>
+        <v>0.1705843534510285</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2411937522746653</v>
+        <v>0.2430937522746653</v>
       </c>
       <c r="C25">
-        <v>14.76241317991835</v>
+        <v>14.3047239235645</v>
       </c>
       <c r="D25">
-        <v>20.36375317991835</v>
+        <v>20.1676439235645</v>
       </c>
       <c r="E25">
-        <v>5.958340000000001</v>
+        <v>6.219920000000001</v>
       </c>
       <c r="F25">
-        <v>6.01634</v>
+        <v>6.277920000000001</v>
       </c>
       <c r="G25">
         <v>0.415</v>
@@ -3465,37 +3465,37 @@
         <v>0.242</v>
       </c>
       <c r="M25">
-        <v>1.418652972</v>
+        <v>1.480333536</v>
       </c>
       <c r="N25">
-        <v>-1.176652972</v>
+        <v>-1.238333536</v>
       </c>
       <c r="O25">
-        <v>-0.20003100524</v>
+        <v>-0.2105167011200001</v>
       </c>
       <c r="P25">
-        <v>-0.97662196676</v>
+        <v>-1.02781683488</v>
       </c>
       <c r="Q25">
-        <v>-0.85962196676</v>
+        <v>-0.9108168348800003</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2448474058245793</v>
+        <v>0.2474664506380606</v>
       </c>
       <c r="T25">
-        <v>0.7128524315033857</v>
+        <v>0.7222320687600092</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.02899934008667484</v>
+        <v>0.02779103424973005</v>
       </c>
       <c r="W25">
-        <v>0.2289619556075621</v>
+        <v>0.2292468741239137</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1705843534510285</v>
+        <v>0.1634766720572356</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2430937522746653</v>
+        <v>0.2449937522746653</v>
       </c>
       <c r="C26">
-        <v>14.3047239235645</v>
+        <v>13.85077582457947</v>
       </c>
       <c r="D26">
-        <v>20.1676439235645</v>
+        <v>19.97527582457947</v>
       </c>
       <c r="E26">
-        <v>6.21992</v>
+        <v>6.4815</v>
       </c>
       <c r="F26">
-        <v>6.27792</v>
+        <v>6.5395</v>
       </c>
       <c r="G26">
         <v>0.415</v>
@@ -3547,37 +3547,37 @@
         <v>0.242</v>
       </c>
       <c r="M26">
-        <v>1.480333536</v>
+        <v>1.5420141</v>
       </c>
       <c r="N26">
-        <v>-1.238333536</v>
+        <v>-1.3000141</v>
       </c>
       <c r="O26">
-        <v>-0.21051670112</v>
+        <v>-0.221002397</v>
       </c>
       <c r="P26">
-        <v>-1.02781683488</v>
+        <v>-1.079011703</v>
       </c>
       <c r="Q26">
-        <v>-0.9108168348800001</v>
+        <v>-0.9620117029999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2474664506380606</v>
+        <v>0.250155336646568</v>
       </c>
       <c r="T26">
-        <v>0.7222320687600092</v>
+        <v>0.7318618296768092</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.02779103424973006</v>
+        <v>0.02667939287974085</v>
       </c>
       <c r="W26">
-        <v>0.2292468741239137</v>
+        <v>0.2295089991589571</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1634766720572356</v>
+        <v>0.1569376051749461</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2449937522746653</v>
+        <v>0.2468937522746653</v>
       </c>
       <c r="C27">
-        <v>13.85077582457947</v>
+        <v>13.40046283990244</v>
       </c>
       <c r="D27">
-        <v>19.97527582457947</v>
+        <v>19.78654283990244</v>
       </c>
       <c r="E27">
-        <v>6.4815</v>
+        <v>6.743080000000001</v>
       </c>
       <c r="F27">
-        <v>6.5395</v>
+        <v>6.801080000000001</v>
       </c>
       <c r="G27">
         <v>0.415</v>
@@ -3629,37 +3629,37 @@
         <v>0.242</v>
       </c>
       <c r="M27">
-        <v>1.5420141</v>
+        <v>1.603694664</v>
       </c>
       <c r="N27">
-        <v>-1.3000141</v>
+        <v>-1.361694664</v>
       </c>
       <c r="O27">
-        <v>-0.221002397</v>
+        <v>-0.2314880928800001</v>
       </c>
       <c r="P27">
-        <v>-1.079011703</v>
+        <v>-1.13020657112</v>
       </c>
       <c r="Q27">
-        <v>-0.9620117029999999</v>
+        <v>-1.01320657112</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.250155336646568</v>
+        <v>0.2529168952499001</v>
       </c>
       <c r="T27">
-        <v>0.7318618296768092</v>
+        <v>0.7417518544021717</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.02667939287974085</v>
+        <v>0.0256532623843662</v>
       </c>
       <c r="W27">
-        <v>0.2295089991589571</v>
+        <v>0.2297509607297665</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1569376051749461</v>
+        <v>0.1509015434374482</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2468937522746653</v>
+        <v>0.2487937522746653</v>
       </c>
       <c r="C28">
-        <v>13.40046283990244</v>
+        <v>12.95368289667982</v>
       </c>
       <c r="D28">
-        <v>19.78654283990244</v>
+        <v>19.60134289667982</v>
       </c>
       <c r="E28">
-        <v>6.743080000000001</v>
+        <v>7.004660000000001</v>
       </c>
       <c r="F28">
-        <v>6.801080000000001</v>
+        <v>7.062660000000001</v>
       </c>
       <c r="G28">
         <v>0.415</v>
@@ -3711,37 +3711,37 @@
         <v>0.242</v>
       </c>
       <c r="M28">
-        <v>1.603694664</v>
+        <v>1.665375228</v>
       </c>
       <c r="N28">
-        <v>-1.361694664</v>
+        <v>-1.423375228</v>
       </c>
       <c r="O28">
-        <v>-0.2314880928800001</v>
+        <v>-0.2419737887600001</v>
       </c>
       <c r="P28">
-        <v>-1.13020657112</v>
+        <v>-1.18140143924</v>
       </c>
       <c r="Q28">
-        <v>-1.01320657112</v>
+        <v>-1.06440143924</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2529168952499001</v>
+        <v>0.2557541129930493</v>
       </c>
       <c r="T28">
-        <v>0.7417518544021717</v>
+        <v>0.7519128387090507</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.0256532623843662</v>
+        <v>0.0247031415553156</v>
       </c>
       <c r="W28">
-        <v>0.2297509607297665</v>
+        <v>0.2299749992212566</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1509015434374482</v>
+        <v>0.1453125973842094</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2487937522746653</v>
+        <v>0.2506937522746653</v>
       </c>
       <c r="C29">
-        <v>12.95368289667982</v>
+        <v>12.51033770818463</v>
       </c>
       <c r="D29">
-        <v>19.60134289667982</v>
+        <v>19.41957770818463</v>
       </c>
       <c r="E29">
-        <v>7.004660000000001</v>
+        <v>7.266240000000002</v>
       </c>
       <c r="F29">
-        <v>7.062660000000001</v>
+        <v>7.324240000000001</v>
       </c>
       <c r="G29">
         <v>0.415</v>
@@ -3793,37 +3793,37 @@
         <v>0.242</v>
       </c>
       <c r="M29">
-        <v>1.665375228</v>
+        <v>1.727055792</v>
       </c>
       <c r="N29">
-        <v>-1.423375228</v>
+        <v>-1.485055792</v>
       </c>
       <c r="O29">
-        <v>-0.2419737887600001</v>
+        <v>-0.2524594846400001</v>
       </c>
       <c r="P29">
-        <v>-1.18140143924</v>
+        <v>-1.23259630736</v>
       </c>
       <c r="Q29">
-        <v>-1.06440143924</v>
+        <v>-1.11559630736</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2557541129930493</v>
+        <v>0.258670142340175</v>
       </c>
       <c r="T29">
-        <v>0.7519128387090507</v>
+        <v>0.7623560725800098</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.0247031415553156</v>
+        <v>0.02382088649976861</v>
       </c>
       <c r="W29">
-        <v>0.2299749992212566</v>
+        <v>0.2301830349633546</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1453125973842094</v>
+        <v>0.1401228617633448</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2506937522746653</v>
+        <v>0.2525937522746653</v>
       </c>
       <c r="C30">
-        <v>12.51033770818463</v>
+        <v>12.07033259988376</v>
       </c>
       <c r="D30">
-        <v>19.41957770818463</v>
+        <v>19.24115259988376</v>
       </c>
       <c r="E30">
-        <v>7.266240000000002</v>
+        <v>7.527820000000001</v>
       </c>
       <c r="F30">
-        <v>7.324240000000001</v>
+        <v>7.585820000000001</v>
       </c>
       <c r="G30">
         <v>0.415</v>
@@ -3875,37 +3875,37 @@
         <v>0.242</v>
       </c>
       <c r="M30">
-        <v>1.727055792</v>
+        <v>1.788736356</v>
       </c>
       <c r="N30">
-        <v>-1.485055792</v>
+        <v>-1.546736356</v>
       </c>
       <c r="O30">
-        <v>-0.2524594846400001</v>
+        <v>-0.26294518052</v>
       </c>
       <c r="P30">
-        <v>-1.23259630736</v>
+        <v>-1.28379117548</v>
       </c>
       <c r="Q30">
-        <v>-1.11559630736</v>
+        <v>-1.16679117548</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.258670142340175</v>
+        <v>0.2616683133590507</v>
       </c>
       <c r="T30">
-        <v>0.7623560725800098</v>
+        <v>0.7730934820529676</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.02382088649976861</v>
+        <v>0.02299947662046625</v>
       </c>
       <c r="W30">
-        <v>0.2301830349633546</v>
+        <v>0.2303767234128941</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1401228617633448</v>
+        <v>0.1352910389439191</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2525937522746653</v>
+        <v>0.2544937522746653</v>
       </c>
       <c r="C31">
-        <v>12.07033259988376</v>
+        <v>11.6335763450064</v>
       </c>
       <c r="D31">
-        <v>19.24115259988376</v>
+        <v>19.0659763450064</v>
       </c>
       <c r="E31">
-        <v>7.52782</v>
+        <v>7.789400000000001</v>
       </c>
       <c r="F31">
-        <v>7.58582</v>
+        <v>7.8474</v>
       </c>
       <c r="G31">
         <v>0.415</v>
@@ -3957,37 +3957,37 @@
         <v>0.242</v>
       </c>
       <c r="M31">
-        <v>1.788736356</v>
+        <v>1.85041692</v>
       </c>
       <c r="N31">
-        <v>-1.546736356</v>
+        <v>-1.60841692</v>
       </c>
       <c r="O31">
-        <v>-0.26294518052</v>
+        <v>-0.2734308764000001</v>
       </c>
       <c r="P31">
-        <v>-1.28379117548</v>
+        <v>-1.3349860436</v>
       </c>
       <c r="Q31">
-        <v>-1.16679117548</v>
+        <v>-1.2179860436</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2616683133590507</v>
+        <v>0.2647521464070372</v>
       </c>
       <c r="T31">
-        <v>0.7730934820529676</v>
+        <v>0.7841376746537243</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.02299947662046626</v>
+        <v>0.02223282739978404</v>
       </c>
       <c r="W31">
-        <v>0.2303767234128941</v>
+        <v>0.2305574992991309</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1352910389439191</v>
+        <v>0.1307813376457885</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2544937522746653</v>
+        <v>0.2563937522746653</v>
       </c>
       <c r="C32">
-        <v>11.6335763450064</v>
+        <v>11.19998100901359</v>
       </c>
       <c r="D32">
-        <v>19.0659763450064</v>
+        <v>18.89396100901359</v>
       </c>
       <c r="E32">
-        <v>7.789400000000001</v>
+        <v>8.050980000000001</v>
       </c>
       <c r="F32">
-        <v>7.8474</v>
+        <v>8.108980000000001</v>
       </c>
       <c r="G32">
         <v>0.415</v>
@@ -4039,37 +4039,37 @@
         <v>0.242</v>
       </c>
       <c r="M32">
-        <v>1.85041692</v>
+        <v>1.912097484</v>
       </c>
       <c r="N32">
-        <v>-1.60841692</v>
+        <v>-1.670097484</v>
       </c>
       <c r="O32">
-        <v>-0.2734308764000001</v>
+        <v>-0.2839165722800001</v>
       </c>
       <c r="P32">
-        <v>-1.3349860436</v>
+        <v>-1.38618091172</v>
       </c>
       <c r="Q32">
-        <v>-1.2179860436</v>
+        <v>-1.26918091172</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2647521464070372</v>
+        <v>0.2679253659201827</v>
       </c>
       <c r="T32">
-        <v>0.7841376746537243</v>
+        <v>0.7955019887791406</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.02223282739978404</v>
+        <v>0.02151563941914585</v>
       </c>
       <c r="W32">
-        <v>0.2305574992991309</v>
+        <v>0.2307266122249654</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1307813376457885</v>
+        <v>0.126562584818505</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2563937522746653</v>
+        <v>0.2582937522746653</v>
       </c>
       <c r="C33">
-        <v>11.19998100901359</v>
+        <v>10.76946180241177</v>
       </c>
       <c r="D33">
-        <v>18.89396100901359</v>
+        <v>18.72502180241177</v>
       </c>
       <c r="E33">
-        <v>8.050980000000001</v>
+        <v>8.312560000000001</v>
       </c>
       <c r="F33">
-        <v>8.108980000000001</v>
+        <v>8.370560000000001</v>
       </c>
       <c r="G33">
         <v>0.415</v>
@@ -4121,37 +4121,37 @@
         <v>0.242</v>
       </c>
       <c r="M33">
-        <v>1.912097484</v>
+        <v>1.973778048</v>
       </c>
       <c r="N33">
-        <v>-1.670097484</v>
+        <v>-1.731778048</v>
       </c>
       <c r="O33">
-        <v>-0.2839165722800001</v>
+        <v>-0.2944022681600001</v>
       </c>
       <c r="P33">
-        <v>-1.38618091172</v>
+        <v>-1.43737577984</v>
       </c>
       <c r="Q33">
-        <v>-1.26918091172</v>
+        <v>-1.32037577984</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2679253659201827</v>
+        <v>0.2711919154190089</v>
       </c>
       <c r="T33">
-        <v>0.7955019887791406</v>
+        <v>0.8072005474376573</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.02151563941914585</v>
+        <v>0.02084327568729754</v>
       </c>
       <c r="W33">
-        <v>0.2307266122249654</v>
+        <v>0.2308851555929353</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.126562584818505</v>
+        <v>0.1226075040429266</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2582937522746653</v>
+        <v>0.2601937522746653</v>
       </c>
       <c r="C34">
-        <v>10.76946180241177</v>
+        <v>10.34193694139267</v>
       </c>
       <c r="D34">
-        <v>18.72502180241177</v>
+        <v>18.55907694139268</v>
       </c>
       <c r="E34">
-        <v>8.312560000000001</v>
+        <v>8.574140000000002</v>
       </c>
       <c r="F34">
-        <v>8.370560000000001</v>
+        <v>8.632140000000001</v>
       </c>
       <c r="G34">
         <v>0.415</v>
@@ -4203,37 +4203,37 @@
         <v>0.242</v>
       </c>
       <c r="M34">
-        <v>1.973778048</v>
+        <v>2.035458612</v>
       </c>
       <c r="N34">
-        <v>-1.731778048</v>
+        <v>-1.793458612</v>
       </c>
       <c r="O34">
-        <v>-0.2944022681600001</v>
+        <v>-0.3048879640400001</v>
       </c>
       <c r="P34">
-        <v>-1.43737577984</v>
+        <v>-1.48857064796</v>
       </c>
       <c r="Q34">
-        <v>-1.32037577984</v>
+        <v>-1.37157064796</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2711919154190089</v>
+        <v>0.2745559738580985</v>
       </c>
       <c r="T34">
-        <v>0.8072005474376573</v>
+        <v>0.8192483168023985</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02084327568729754</v>
+        <v>0.02021166127253095</v>
       </c>
       <c r="W34">
-        <v>0.2308851555929353</v>
+        <v>0.2310340902719372</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1226075040429266</v>
+        <v>0.118892125132535</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2601937522746653</v>
+        <v>0.2620937522746653</v>
       </c>
       <c r="C35">
-        <v>10.34193694139267</v>
+        <v>9.917327515818386</v>
       </c>
       <c r="D35">
-        <v>18.55907694139268</v>
+        <v>18.39604751581839</v>
       </c>
       <c r="E35">
-        <v>8.574140000000002</v>
+        <v>8.835720000000002</v>
       </c>
       <c r="F35">
-        <v>8.632140000000001</v>
+        <v>8.893720000000002</v>
       </c>
       <c r="G35">
         <v>0.415</v>
@@ -4285,37 +4285,37 @@
         <v>0.242</v>
       </c>
       <c r="M35">
-        <v>2.035458612</v>
+        <v>2.097139176000001</v>
       </c>
       <c r="N35">
-        <v>-1.793458612</v>
+        <v>-1.855139176000001</v>
       </c>
       <c r="O35">
-        <v>-0.3048879640400001</v>
+        <v>-0.3153736599200002</v>
       </c>
       <c r="P35">
-        <v>-1.48857064796</v>
+        <v>-1.539765516080001</v>
       </c>
       <c r="Q35">
-        <v>-1.37157064796</v>
+        <v>-1.422765516080001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2745559738580985</v>
+        <v>0.2780219734620091</v>
       </c>
       <c r="T35">
-        <v>0.8192483168023985</v>
+        <v>0.8316611700872834</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02021166127253095</v>
+        <v>0.01961720064686827</v>
       </c>
       <c r="W35">
-        <v>0.2310340902719372</v>
+        <v>0.2311742640874685</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.118892125132535</v>
+        <v>0.1153952979227545</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2620937522746653</v>
+        <v>0.2639937522746653</v>
       </c>
       <c r="C36">
-        <v>9.917327515818386</v>
+        <v>9.495557364103792</v>
       </c>
       <c r="D36">
-        <v>18.39604751581839</v>
+        <v>18.23585736410379</v>
       </c>
       <c r="E36">
-        <v>8.835720000000002</v>
+        <v>9.097300000000001</v>
       </c>
       <c r="F36">
-        <v>8.893720000000002</v>
+        <v>9.1553</v>
       </c>
       <c r="G36">
         <v>0.415</v>
@@ -4367,37 +4367,37 @@
         <v>0.242</v>
       </c>
       <c r="M36">
-        <v>2.097139176000001</v>
+        <v>2.15881974</v>
       </c>
       <c r="N36">
-        <v>-1.855139176000001</v>
+        <v>-1.91681974</v>
       </c>
       <c r="O36">
-        <v>-0.3153736599200002</v>
+        <v>-0.3258593558000001</v>
       </c>
       <c r="P36">
-        <v>-1.539765516080001</v>
+        <v>-1.5909603842</v>
       </c>
       <c r="Q36">
-        <v>-1.422765516080001</v>
+        <v>-1.4739603842</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2780219734620091</v>
+        <v>0.2815946192075785</v>
       </c>
       <c r="T36">
-        <v>0.8316611700872834</v>
+        <v>0.8444559573193954</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.01961720064686827</v>
+        <v>0.0190567091998149</v>
       </c>
       <c r="W36">
-        <v>0.2311742640874685</v>
+        <v>0.2313064279706837</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1153952979227545</v>
+        <v>0.1120982894106758</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2639937522746653</v>
+        <v>0.2658937522746653</v>
       </c>
       <c r="C37">
-        <v>9.495557364103792</v>
+        <v>9.076552954579624</v>
       </c>
       <c r="D37">
-        <v>18.23585736410379</v>
+        <v>18.07843295457963</v>
       </c>
       <c r="E37">
-        <v>9.097300000000001</v>
+        <v>9.358880000000001</v>
       </c>
       <c r="F37">
-        <v>9.1553</v>
+        <v>9.416880000000001</v>
       </c>
       <c r="G37">
         <v>0.415</v>
@@ -4449,37 +4449,37 @@
         <v>0.242</v>
       </c>
       <c r="M37">
-        <v>2.15881974</v>
+        <v>2.220500304</v>
       </c>
       <c r="N37">
-        <v>-1.91681974</v>
+        <v>-1.978500304</v>
       </c>
       <c r="O37">
-        <v>-0.3258593558000001</v>
+        <v>-0.3363450516800001</v>
       </c>
       <c r="P37">
-        <v>-1.5909603842</v>
+        <v>-1.64215525232</v>
       </c>
       <c r="Q37">
-        <v>-1.4739603842</v>
+        <v>-1.52515525232</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2815946192075785</v>
+        <v>0.285278910132697</v>
       </c>
       <c r="T37">
-        <v>0.8444559573193954</v>
+        <v>0.8576505816525111</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0190567091998149</v>
+        <v>0.0185273561664867</v>
       </c>
       <c r="W37">
-        <v>0.2313064279706837</v>
+        <v>0.2314312494159425</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1120982894106758</v>
+        <v>0.1089844480381571</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2658937522746653</v>
+        <v>0.2677937522746653</v>
       </c>
       <c r="C38">
-        <v>9.076552954579627</v>
+        <v>8.660243272947856</v>
       </c>
       <c r="D38">
-        <v>18.07843295457963</v>
+        <v>17.92370327294786</v>
       </c>
       <c r="E38">
-        <v>9.358880000000001</v>
+        <v>9.620460000000001</v>
       </c>
       <c r="F38">
-        <v>9.416880000000001</v>
+        <v>9.678460000000001</v>
       </c>
       <c r="G38">
         <v>0.415</v>
@@ -4531,37 +4531,37 @@
         <v>0.242</v>
       </c>
       <c r="M38">
-        <v>2.220500304</v>
+        <v>2.282180868</v>
       </c>
       <c r="N38">
-        <v>-1.978500304</v>
+        <v>-2.040180868</v>
       </c>
       <c r="O38">
-        <v>-0.3363450516800001</v>
+        <v>-0.34683074756</v>
       </c>
       <c r="P38">
-        <v>-1.64215525232</v>
+        <v>-1.69335012044</v>
       </c>
       <c r="Q38">
-        <v>-1.52515525232</v>
+        <v>-1.57635012044</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2852789101326969</v>
+        <v>0.2890801626744858</v>
       </c>
       <c r="T38">
-        <v>0.8576505816525108</v>
+        <v>0.8712640829485826</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.0185273561664867</v>
+        <v>0.01802661681063571</v>
       </c>
       <c r="W38">
-        <v>0.2314312494159425</v>
+        <v>0.2315493237560521</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1089844480381571</v>
+        <v>0.1060389224155042</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2677937522746653</v>
+        <v>0.2696937522746653</v>
       </c>
       <c r="C39">
-        <v>8.660243272947856</v>
+        <v>8.246559715467502</v>
       </c>
       <c r="D39">
-        <v>17.92370327294786</v>
+        <v>17.7715997154675</v>
       </c>
       <c r="E39">
-        <v>9.620460000000001</v>
+        <v>9.88204</v>
       </c>
       <c r="F39">
-        <v>9.678460000000001</v>
+        <v>9.94004</v>
       </c>
       <c r="G39">
         <v>0.415</v>
@@ -4613,37 +4613,37 @@
         <v>0.242</v>
       </c>
       <c r="M39">
-        <v>2.282180868</v>
+        <v>2.343861432</v>
       </c>
       <c r="N39">
-        <v>-2.040180868</v>
+        <v>-2.101861432</v>
       </c>
       <c r="O39">
-        <v>-0.34683074756</v>
+        <v>-0.3573164434400001</v>
       </c>
       <c r="P39">
-        <v>-1.69335012044</v>
+        <v>-1.74454498856</v>
       </c>
       <c r="Q39">
-        <v>-1.57635012044</v>
+        <v>-1.62754498856</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2890801626744858</v>
+        <v>0.2930040362660097</v>
       </c>
       <c r="T39">
-        <v>0.8712640829485826</v>
+        <v>0.8853167294477532</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.01802661681063571</v>
+        <v>0.01755223215772424</v>
       </c>
       <c r="W39">
-        <v>0.2315493237560521</v>
+        <v>0.2316611836572086</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1060389224155042</v>
+        <v>0.1032484244572014</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2696937522746653</v>
+        <v>0.2715937522746653</v>
       </c>
       <c r="C40">
-        <v>8.246559715467502</v>
+        <v>7.835435987533375</v>
       </c>
       <c r="D40">
-        <v>17.7715997154675</v>
+        <v>17.62205598753338</v>
       </c>
       <c r="E40">
-        <v>9.88204</v>
+        <v>10.14362</v>
       </c>
       <c r="F40">
-        <v>9.94004</v>
+        <v>10.20162</v>
       </c>
       <c r="G40">
         <v>0.415</v>
@@ -4695,37 +4695,37 @@
         <v>0.242</v>
       </c>
       <c r="M40">
-        <v>2.343861432</v>
+        <v>2.405541996</v>
       </c>
       <c r="N40">
-        <v>-2.101861432</v>
+        <v>-2.163541996</v>
       </c>
       <c r="O40">
-        <v>-0.3573164434400001</v>
+        <v>-0.3678021393200001</v>
       </c>
       <c r="P40">
-        <v>-1.74454498856</v>
+        <v>-1.79573985668</v>
       </c>
       <c r="Q40">
-        <v>-1.62754498856</v>
+        <v>-1.67873985668</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2930040362660097</v>
+        <v>0.2970565614506984</v>
       </c>
       <c r="T40">
-        <v>0.8853167294477532</v>
+        <v>0.8998301184550934</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.01755223215772424</v>
+        <v>0.0171021749229108</v>
       </c>
       <c r="W40">
-        <v>0.2316611836572086</v>
+        <v>0.2317673071531776</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1032484244572014</v>
+        <v>0.1006010289582988</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2715937522746653</v>
+        <v>0.2734937522746653</v>
       </c>
       <c r="C41">
-        <v>7.835435987533375</v>
+        <v>7.426808007332653</v>
       </c>
       <c r="D41">
-        <v>17.62205598753338</v>
+        <v>17.47500800733265</v>
       </c>
       <c r="E41">
-        <v>10.14362</v>
+        <v>10.4052</v>
       </c>
       <c r="F41">
-        <v>10.20162</v>
+        <v>10.4632</v>
       </c>
       <c r="G41">
         <v>0.415</v>
@@ -4777,37 +4777,37 @@
         <v>0.242</v>
       </c>
       <c r="M41">
-        <v>2.405541996</v>
+        <v>2.46722256</v>
       </c>
       <c r="N41">
-        <v>-2.163541996</v>
+        <v>-2.22522256</v>
       </c>
       <c r="O41">
-        <v>-0.3678021393200001</v>
+        <v>-0.3782878352</v>
       </c>
       <c r="P41">
-        <v>-1.79573985668</v>
+        <v>-1.8469347248</v>
       </c>
       <c r="Q41">
-        <v>-1.67873985668</v>
+        <v>-1.7299347248</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2970565614506984</v>
+        <v>0.3012441708082101</v>
       </c>
       <c r="T41">
-        <v>0.8998301184550934</v>
+        <v>0.9148272870960117</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0171021749229108</v>
+        <v>0.01667462054983803</v>
       </c>
       <c r="W41">
-        <v>0.2317673071531776</v>
+        <v>0.2318681244743482</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1006010289582988</v>
+        <v>0.09808600323434136</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2734937522746653</v>
+        <v>0.2753937522746653</v>
       </c>
       <c r="C42">
-        <v>7.426808007332653</v>
+        <v>7.020613814285221</v>
       </c>
       <c r="D42">
-        <v>17.47500800733265</v>
+        <v>17.33039381428522</v>
       </c>
       <c r="E42">
-        <v>10.4052</v>
+        <v>10.66678</v>
       </c>
       <c r="F42">
-        <v>10.4632</v>
+        <v>10.72478</v>
       </c>
       <c r="G42">
         <v>0.415</v>
@@ -4859,37 +4859,37 @@
         <v>0.242</v>
       </c>
       <c r="M42">
-        <v>2.46722256</v>
+        <v>2.528903124</v>
       </c>
       <c r="N42">
-        <v>-2.22522256</v>
+        <v>-2.286903124</v>
       </c>
       <c r="O42">
-        <v>-0.3782878352</v>
+        <v>-0.3887735310800001</v>
       </c>
       <c r="P42">
-        <v>-1.8469347248</v>
+        <v>-1.89812959292</v>
       </c>
       <c r="Q42">
-        <v>-1.7299347248</v>
+        <v>-1.78112959292</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3012441708082101</v>
+        <v>0.3055737330252984</v>
       </c>
       <c r="T42">
-        <v>0.9148272870960117</v>
+        <v>0.9303328343349272</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.01667462054983803</v>
+        <v>0.01626792248764686</v>
       </c>
       <c r="W42">
-        <v>0.2318681244743482</v>
+        <v>0.2319640238774129</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.09808600323434136</v>
+        <v>0.0956936616920403</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2753937522746653</v>
+        <v>0.2772937522746653</v>
       </c>
       <c r="C43">
-        <v>7.020613814285221</v>
+        <v>6.616793481992914</v>
       </c>
       <c r="D43">
-        <v>17.33039381428522</v>
+        <v>17.18815348199292</v>
       </c>
       <c r="E43">
-        <v>10.66678</v>
+        <v>10.92836</v>
       </c>
       <c r="F43">
-        <v>10.72478</v>
+        <v>10.98636</v>
       </c>
       <c r="G43">
         <v>0.415</v>
@@ -4941,37 +4941,37 @@
         <v>0.242</v>
       </c>
       <c r="M43">
-        <v>2.528903124</v>
+        <v>2.590583688000001</v>
       </c>
       <c r="N43">
-        <v>-2.286903124</v>
+        <v>-2.348583688000001</v>
       </c>
       <c r="O43">
-        <v>-0.3887735310800001</v>
+        <v>-0.3992592269600002</v>
       </c>
       <c r="P43">
-        <v>-1.89812959292</v>
+        <v>-1.94932446104</v>
       </c>
       <c r="Q43">
-        <v>-1.78112959292</v>
+        <v>-1.83232446104</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3055737330252984</v>
+        <v>0.3100525904912518</v>
       </c>
       <c r="T43">
-        <v>0.9303328343349272</v>
+        <v>0.9463730556165638</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.01626792248764686</v>
+        <v>0.01588059099984574</v>
       </c>
       <c r="W43">
-        <v>0.2319640238774129</v>
+        <v>0.2320553566422364</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.0956936616920403</v>
+        <v>0.09341524117556321</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2772937522746654</v>
+        <v>0.2791937522746654</v>
       </c>
       <c r="C44">
-        <v>6.616793481992913</v>
+        <v>6.215289035440655</v>
       </c>
       <c r="D44">
-        <v>17.18815348199291</v>
+        <v>17.04822903544066</v>
       </c>
       <c r="E44">
-        <v>10.92836</v>
+        <v>11.18994</v>
       </c>
       <c r="F44">
-        <v>10.98636</v>
+        <v>11.24794</v>
       </c>
       <c r="G44">
         <v>0.415</v>
@@ -5023,37 +5023,37 @@
         <v>0.242</v>
       </c>
       <c r="M44">
-        <v>2.590583688</v>
+        <v>2.652264252</v>
       </c>
       <c r="N44">
-        <v>-2.348583688</v>
+        <v>-2.410264252</v>
       </c>
       <c r="O44">
-        <v>-0.39925922696</v>
+        <v>-0.4097449228400001</v>
       </c>
       <c r="P44">
-        <v>-1.94932446104</v>
+        <v>-2.00051932916</v>
       </c>
       <c r="Q44">
-        <v>-1.83232446104</v>
+        <v>-1.88351932916</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3100525904912518</v>
+        <v>0.3146886008507475</v>
       </c>
       <c r="T44">
-        <v>0.9463730556165637</v>
+        <v>0.9629760916800123</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01588059099984574</v>
+        <v>0.01551127493008189</v>
       </c>
       <c r="W44">
-        <v>0.2320553566422364</v>
+        <v>0.2321424413714867</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.09341524117556321</v>
+        <v>0.09124279370636401</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2791937522746654</v>
+        <v>0.2810937522746653</v>
       </c>
       <c r="C45">
-        <v>6.215289035440655</v>
+        <v>5.816044372209289</v>
       </c>
       <c r="D45">
-        <v>17.04822903544066</v>
+        <v>16.91056437220929</v>
       </c>
       <c r="E45">
-        <v>11.18994</v>
+        <v>11.45152</v>
       </c>
       <c r="F45">
-        <v>11.24794</v>
+        <v>11.50952</v>
       </c>
       <c r="G45">
         <v>0.415</v>
@@ -5105,37 +5105,37 @@
         <v>0.242</v>
       </c>
       <c r="M45">
-        <v>2.652264252</v>
+        <v>2.713944816</v>
       </c>
       <c r="N45">
-        <v>-2.410264252</v>
+        <v>-2.471944816</v>
       </c>
       <c r="O45">
-        <v>-0.4097449228400001</v>
+        <v>-0.4202306187200001</v>
       </c>
       <c r="P45">
-        <v>-2.00051932916</v>
+        <v>-2.05171419728</v>
       </c>
       <c r="Q45">
-        <v>-1.88351932916</v>
+        <v>-1.93471419728</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3146886008507475</v>
+        <v>0.3194901830087965</v>
       </c>
       <c r="T45">
-        <v>0.9629760916800123</v>
+        <v>0.9801720933171553</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01551127493008189</v>
+        <v>0.01515874595439821</v>
       </c>
       <c r="W45">
-        <v>0.2321424413714867</v>
+        <v>0.2322255677039529</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.09124279370636401</v>
+        <v>0.08916909384940119</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2810937522746653</v>
+        <v>0.2829937522746653</v>
       </c>
       <c r="C46">
-        <v>5.816044372209289</v>
+        <v>5.41900518747498</v>
       </c>
       <c r="D46">
-        <v>16.91056437220929</v>
+        <v>16.77510518747498</v>
       </c>
       <c r="E46">
-        <v>11.45152</v>
+        <v>11.7131</v>
       </c>
       <c r="F46">
-        <v>11.50952</v>
+        <v>11.7711</v>
       </c>
       <c r="G46">
         <v>0.415</v>
@@ -5187,37 +5187,37 @@
         <v>0.242</v>
       </c>
       <c r="M46">
-        <v>2.713944816</v>
+        <v>2.77562538</v>
       </c>
       <c r="N46">
-        <v>-2.471944816</v>
+        <v>-2.53362538</v>
       </c>
       <c r="O46">
-        <v>-0.4202306187200001</v>
+        <v>-0.4307163146</v>
       </c>
       <c r="P46">
-        <v>-2.05171419728</v>
+        <v>-2.1029090654</v>
       </c>
       <c r="Q46">
-        <v>-1.93471419728</v>
+        <v>-1.9859090654</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3194901830087965</v>
+        <v>0.324466368154411</v>
       </c>
       <c r="T46">
-        <v>0.9801720933171553</v>
+        <v>0.99799340410474</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01515874595439821</v>
+        <v>0.01482188493318936</v>
       </c>
       <c r="W46">
-        <v>0.2322255677039529</v>
+        <v>0.232304999532754</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.08916909384940119</v>
+        <v>0.08718755843052561</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2829937522746653</v>
+        <v>0.2848937522746653</v>
       </c>
       <c r="C47">
-        <v>5.41900518747498</v>
+        <v>5.024118902584741</v>
       </c>
       <c r="D47">
-        <v>16.77510518747498</v>
+        <v>16.64179890258474</v>
       </c>
       <c r="E47">
-        <v>11.7131</v>
+        <v>11.97468</v>
       </c>
       <c r="F47">
-        <v>11.7711</v>
+        <v>12.03268</v>
       </c>
       <c r="G47">
         <v>0.415</v>
@@ -5269,37 +5269,37 @@
         <v>0.242</v>
       </c>
       <c r="M47">
-        <v>2.77562538</v>
+        <v>2.837305944</v>
       </c>
       <c r="N47">
-        <v>-2.53362538</v>
+        <v>-2.595305944</v>
       </c>
       <c r="O47">
-        <v>-0.4307163146</v>
+        <v>-0.4412020104800001</v>
       </c>
       <c r="P47">
-        <v>-2.1029090654</v>
+        <v>-2.15410393352</v>
       </c>
       <c r="Q47">
-        <v>-1.9859090654</v>
+        <v>-2.03710393352</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.324466368154411</v>
+        <v>0.3296268564535667</v>
       </c>
       <c r="T47">
-        <v>0.99799340410474</v>
+        <v>1.016474763440013</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01482188493318936</v>
+        <v>0.01449967004333742</v>
       </c>
       <c r="W47">
-        <v>0.232304999532754</v>
+        <v>0.2323809778037811</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.08718755843052561</v>
+        <v>0.08529217672551426</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2848937522746653</v>
+        <v>0.2867937522746653</v>
       </c>
       <c r="C48">
-        <v>5.024118902584741</v>
+        <v>4.631334597010575</v>
       </c>
       <c r="D48">
-        <v>16.64179890258474</v>
+        <v>16.51059459701058</v>
       </c>
       <c r="E48">
-        <v>11.97468</v>
+        <v>12.23626</v>
       </c>
       <c r="F48">
-        <v>12.03268</v>
+        <v>12.29426</v>
       </c>
       <c r="G48">
         <v>0.415</v>
@@ -5351,37 +5351,37 @@
         <v>0.242</v>
       </c>
       <c r="M48">
-        <v>2.837305944</v>
+        <v>2.898986508000001</v>
       </c>
       <c r="N48">
-        <v>-2.595305944</v>
+        <v>-2.656986508000001</v>
       </c>
       <c r="O48">
-        <v>-0.4412020104800001</v>
+        <v>-0.4516877063600001</v>
       </c>
       <c r="P48">
-        <v>-2.15410393352</v>
+        <v>-2.205298801640001</v>
       </c>
       <c r="Q48">
-        <v>-2.03710393352</v>
+        <v>-2.088298801640001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3296268564535667</v>
+        <v>0.3349820801602378</v>
       </c>
       <c r="T48">
-        <v>1.016474763440013</v>
+        <v>1.035653532561523</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01449967004333742</v>
+        <v>0.01419116642539407</v>
       </c>
       <c r="W48">
-        <v>0.2323809778037811</v>
+        <v>0.2324537229568921</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.08529217672551426</v>
+        <v>0.08347744956114156</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2867937522746653</v>
+        <v>0.2886937522746653</v>
       </c>
       <c r="C49">
-        <v>4.631334597010575</v>
+        <v>4.240602943497285</v>
       </c>
       <c r="D49">
-        <v>16.51059459701058</v>
+        <v>16.38144294349729</v>
       </c>
       <c r="E49">
-        <v>12.23626</v>
+        <v>12.49784</v>
       </c>
       <c r="F49">
-        <v>12.29426</v>
+        <v>12.55584</v>
       </c>
       <c r="G49">
         <v>0.415</v>
@@ -5433,37 +5433,37 @@
         <v>0.242</v>
       </c>
       <c r="M49">
-        <v>2.898986508000001</v>
+        <v>2.960667072000001</v>
       </c>
       <c r="N49">
-        <v>-2.656986508000001</v>
+        <v>-2.718667072000001</v>
       </c>
       <c r="O49">
-        <v>-0.4516877063600001</v>
+        <v>-0.4621734022400001</v>
       </c>
       <c r="P49">
-        <v>-2.205298801640001</v>
+        <v>-2.25649366976</v>
       </c>
       <c r="Q49">
-        <v>-2.088298801640001</v>
+        <v>-2.13949366976</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3349820801602378</v>
+        <v>0.3405432740094731</v>
       </c>
       <c r="T49">
-        <v>1.035653532561523</v>
+        <v>1.055569946649244</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01419116642539407</v>
+        <v>0.01389551712486503</v>
       </c>
       <c r="W49">
-        <v>0.2324537229568921</v>
+        <v>0.2325234370619568</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.08347744956114156</v>
+        <v>0.0817383360286178</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2886937522746653</v>
+        <v>0.2905937522746653</v>
       </c>
       <c r="C50">
-        <v>4.240602943497287</v>
+        <v>3.851876146230493</v>
       </c>
       <c r="D50">
-        <v>16.38144294349729</v>
+        <v>16.25429614623049</v>
       </c>
       <c r="E50">
-        <v>12.49784</v>
+        <v>12.75942</v>
       </c>
       <c r="F50">
-        <v>12.55584</v>
+        <v>12.81742</v>
       </c>
       <c r="G50">
         <v>0.415</v>
@@ -5515,37 +5515,37 @@
         <v>0.242</v>
       </c>
       <c r="M50">
-        <v>2.960667072</v>
+        <v>3.022347636</v>
       </c>
       <c r="N50">
-        <v>-2.718667072</v>
+        <v>-2.780347636</v>
       </c>
       <c r="O50">
-        <v>-0.46217340224</v>
+        <v>-0.4726590981200001</v>
       </c>
       <c r="P50">
-        <v>-2.25649366976</v>
+        <v>-2.30768853788</v>
       </c>
       <c r="Q50">
-        <v>-2.13949366976</v>
+        <v>-2.19068853788</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3405432740094731</v>
+        <v>0.3463225538920118</v>
       </c>
       <c r="T50">
-        <v>1.055569946649244</v>
+        <v>1.076267396583543</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01389551712486503</v>
+        <v>0.01361193514272492</v>
       </c>
       <c r="W50">
-        <v>0.2325234370619568</v>
+        <v>0.2325903056933455</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.0817383360286178</v>
+        <v>0.08007020672191134</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2905937522746653</v>
+        <v>0.2924937522746653</v>
       </c>
       <c r="C51">
-        <v>3.851876146230493</v>
+        <v>3.465107881861908</v>
       </c>
       <c r="D51">
-        <v>16.25429614623049</v>
+        <v>16.12910788186191</v>
       </c>
       <c r="E51">
-        <v>12.75942</v>
+        <v>13.021</v>
       </c>
       <c r="F51">
-        <v>12.81742</v>
+        <v>13.079</v>
       </c>
       <c r="G51">
         <v>0.415</v>
@@ -5597,37 +5597,37 @@
         <v>0.242</v>
       </c>
       <c r="M51">
-        <v>3.022347636</v>
+        <v>3.0840282</v>
       </c>
       <c r="N51">
-        <v>-2.780347636</v>
+        <v>-2.8420282</v>
       </c>
       <c r="O51">
-        <v>-0.4726590981200001</v>
+        <v>-0.483144794</v>
       </c>
       <c r="P51">
-        <v>-2.30768853788</v>
+        <v>-2.358883406</v>
       </c>
       <c r="Q51">
-        <v>-2.19068853788</v>
+        <v>-2.241883406</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3463225538920118</v>
+        <v>0.3523330049698521</v>
       </c>
       <c r="T51">
-        <v>1.076267396583543</v>
+        <v>1.097792744515214</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01361193514272492</v>
+        <v>0.01333969643987043</v>
       </c>
       <c r="W51">
-        <v>0.2325903056933455</v>
+        <v>0.2326544995794786</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.08007020672191134</v>
+        <v>0.07846880258747313</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2924937522746653</v>
+        <v>0.2943937522746653</v>
       </c>
       <c r="C52">
-        <v>3.465107881861908</v>
+        <v>3.08025324323914</v>
       </c>
       <c r="D52">
-        <v>16.12910788186191</v>
+        <v>16.00583324323914</v>
       </c>
       <c r="E52">
-        <v>13.021</v>
+        <v>13.28258</v>
       </c>
       <c r="F52">
-        <v>13.079</v>
+        <v>13.34058</v>
       </c>
       <c r="G52">
         <v>0.415</v>
@@ -5679,37 +5679,37 @@
         <v>0.242</v>
       </c>
       <c r="M52">
-        <v>3.0840282</v>
+        <v>3.145708764000001</v>
       </c>
       <c r="N52">
-        <v>-2.8420282</v>
+        <v>-2.903708764000001</v>
       </c>
       <c r="O52">
-        <v>-0.483144794</v>
+        <v>-0.4936304898800001</v>
       </c>
       <c r="P52">
-        <v>-2.358883406</v>
+        <v>-2.41007827412</v>
       </c>
       <c r="Q52">
-        <v>-2.241883406</v>
+        <v>-2.29307827412</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3523330049698521</v>
+        <v>0.3585887805814817</v>
       </c>
       <c r="T52">
-        <v>1.097792744515214</v>
+        <v>1.120196678076749</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01333969643987043</v>
+        <v>0.01307813376457885</v>
       </c>
       <c r="W52">
-        <v>0.2326544995794786</v>
+        <v>0.2327161760583123</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.07846880258747313</v>
+        <v>0.0769301986151697</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2943937522746653</v>
+        <v>0.2962937522746654</v>
       </c>
       <c r="C53">
-        <v>3.08025324323914</v>
+        <v>2.697268685696287</v>
       </c>
       <c r="D53">
-        <v>16.00583324323914</v>
+        <v>15.88442868569629</v>
       </c>
       <c r="E53">
-        <v>13.28258</v>
+        <v>13.54416</v>
       </c>
       <c r="F53">
-        <v>13.34058</v>
+        <v>13.60216</v>
       </c>
       <c r="G53">
         <v>0.415</v>
@@ -5761,37 +5761,37 @@
         <v>0.242</v>
       </c>
       <c r="M53">
-        <v>3.145708764000001</v>
+        <v>3.207389328000001</v>
       </c>
       <c r="N53">
-        <v>-2.903708764000001</v>
+        <v>-2.965389328000001</v>
       </c>
       <c r="O53">
-        <v>-0.4936304898800001</v>
+        <v>-0.5041161857600002</v>
       </c>
       <c r="P53">
-        <v>-2.41007827412</v>
+        <v>-2.46127314224</v>
       </c>
       <c r="Q53">
-        <v>-2.29307827412</v>
+        <v>-2.34427314224</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3585887805814817</v>
+        <v>0.3651052135102626</v>
       </c>
       <c r="T53">
-        <v>1.120196678076749</v>
+        <v>1.143534108870015</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01307813376457885</v>
+        <v>0.0128266311921831</v>
       </c>
       <c r="W53">
-        <v>0.2327161760583123</v>
+        <v>0.2327754803648832</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.0769301986151697</v>
+        <v>0.07545077171872416</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2962937522746654</v>
+        <v>0.2981937522746654</v>
       </c>
       <c r="C54">
-        <v>2.697268685696287</v>
+        <v>2.31611197577052</v>
       </c>
       <c r="D54">
-        <v>15.88442868569629</v>
+        <v>15.76485197577052</v>
       </c>
       <c r="E54">
-        <v>13.54416</v>
+        <v>13.80574</v>
       </c>
       <c r="F54">
-        <v>13.60216</v>
+        <v>13.86374</v>
       </c>
       <c r="G54">
         <v>0.415</v>
@@ -5843,37 +5843,37 @@
         <v>0.242</v>
       </c>
       <c r="M54">
-        <v>3.207389328000001</v>
+        <v>3.269069892000001</v>
       </c>
       <c r="N54">
-        <v>-2.965389328000001</v>
+        <v>-3.027069892000001</v>
       </c>
       <c r="O54">
-        <v>-0.5041161857600002</v>
+        <v>-0.5146018816400001</v>
       </c>
       <c r="P54">
-        <v>-2.46127314224</v>
+        <v>-2.512468010360001</v>
       </c>
       <c r="Q54">
-        <v>-2.34427314224</v>
+        <v>-2.395468010360001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3651052135102626</v>
+        <v>0.3718989414572895</v>
       </c>
       <c r="T54">
-        <v>1.143534108870015</v>
+        <v>1.167864621824696</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0128266311921831</v>
+        <v>0.01258461928289663</v>
       </c>
       <c r="W54">
-        <v>0.2327754803648832</v>
+        <v>0.232832546773093</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.07545077171872416</v>
+        <v>0.07402717225233313</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2981937522746654</v>
+        <v>0.3000937522746653</v>
       </c>
       <c r="C55">
-        <v>2.31611197577052</v>
+        <v>1.936742142217671</v>
       </c>
       <c r="D55">
-        <v>15.76485197577052</v>
+        <v>15.64706214221767</v>
       </c>
       <c r="E55">
-        <v>13.80574</v>
+        <v>14.06732</v>
       </c>
       <c r="F55">
-        <v>13.86374</v>
+        <v>14.12532</v>
       </c>
       <c r="G55">
         <v>0.415</v>
@@ -5925,37 +5925,37 @@
         <v>0.242</v>
       </c>
       <c r="M55">
-        <v>3.269069892000001</v>
+        <v>3.330750456000001</v>
       </c>
       <c r="N55">
-        <v>-3.027069892000001</v>
+        <v>-3.088750456000001</v>
       </c>
       <c r="O55">
-        <v>-0.5146018816400001</v>
+        <v>-0.5250875775200001</v>
       </c>
       <c r="P55">
-        <v>-2.512468010360001</v>
+        <v>-2.563662878480001</v>
       </c>
       <c r="Q55">
-        <v>-2.395468010360001</v>
+        <v>-2.446662878480001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3718989414572895</v>
+        <v>0.378988048880274</v>
       </c>
       <c r="T55">
-        <v>1.167864621824696</v>
+        <v>1.193252983168711</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01258461928289663</v>
+        <v>0.0123515707776578</v>
       </c>
       <c r="W55">
-        <v>0.232832546773093</v>
+        <v>0.2328874996106283</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.07402717225233313</v>
+        <v>0.07265629869210466</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3000937522746653</v>
+        <v>0.3019937522746653</v>
       </c>
       <c r="C56">
-        <v>1.936742142217671</v>
+        <v>1.559119429207474</v>
       </c>
       <c r="D56">
-        <v>15.64706214221767</v>
+        <v>15.53101942920748</v>
       </c>
       <c r="E56">
-        <v>14.06732</v>
+        <v>14.3289</v>
       </c>
       <c r="F56">
-        <v>14.12532</v>
+        <v>14.3869</v>
       </c>
       <c r="G56">
         <v>0.415</v>
@@ -6007,37 +6007,37 @@
         <v>0.242</v>
       </c>
       <c r="M56">
-        <v>3.330750456000001</v>
+        <v>3.392431020000001</v>
       </c>
       <c r="N56">
-        <v>-3.088750456000001</v>
+        <v>-3.150431020000001</v>
       </c>
       <c r="O56">
-        <v>-0.5250875775200001</v>
+        <v>-0.5355732734000002</v>
       </c>
       <c r="P56">
-        <v>-2.563662878480001</v>
+        <v>-2.6148577466</v>
       </c>
       <c r="Q56">
-        <v>-2.446662878480001</v>
+        <v>-2.4978577466</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.378988048880274</v>
+        <v>0.3863922277442801</v>
       </c>
       <c r="T56">
-        <v>1.193252983168711</v>
+        <v>1.219769716128016</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0123515707776578</v>
+        <v>0.01212699676351857</v>
       </c>
       <c r="W56">
-        <v>0.2328874996106283</v>
+        <v>0.2329404541631623</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.07265629869210466</v>
+        <v>0.07133527507952098</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3019937522746653</v>
+        <v>0.3038937522746653</v>
       </c>
       <c r="C57">
-        <v>1.559119429207474</v>
+        <v>1.183205251586269</v>
       </c>
       <c r="D57">
-        <v>15.53101942920748</v>
+        <v>15.41668525158627</v>
       </c>
       <c r="E57">
-        <v>14.3289</v>
+        <v>14.59048</v>
       </c>
       <c r="F57">
-        <v>14.3869</v>
+        <v>14.64848</v>
       </c>
       <c r="G57">
         <v>0.415</v>
@@ -6089,37 +6089,37 @@
         <v>0.242</v>
       </c>
       <c r="M57">
-        <v>3.392431020000001</v>
+        <v>3.454111584000001</v>
       </c>
       <c r="N57">
-        <v>-3.150431020000001</v>
+        <v>-3.212111584000001</v>
       </c>
       <c r="O57">
-        <v>-0.5355732734000002</v>
+        <v>-0.5460589692800002</v>
       </c>
       <c r="P57">
-        <v>-2.6148577466</v>
+        <v>-2.666052614720001</v>
       </c>
       <c r="Q57">
-        <v>-2.4978577466</v>
+        <v>-2.549052614720001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3863922277442801</v>
+        <v>0.3941329601930137</v>
       </c>
       <c r="T57">
-        <v>1.219769716128016</v>
+        <v>1.247491755130925</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01212699676351857</v>
+        <v>0.01191044324988431</v>
       </c>
       <c r="W57">
-        <v>0.2329404541631623</v>
+        <v>0.2329915174816773</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.07133527507952098</v>
+        <v>0.07006143088167238</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3038937522746653</v>
+        <v>0.3057937522746653</v>
       </c>
       <c r="C58">
-        <v>1.183205251586269</v>
+        <v>0.8089621521012109</v>
       </c>
       <c r="D58">
-        <v>15.41668525158627</v>
+        <v>15.30402215210121</v>
       </c>
       <c r="E58">
-        <v>14.59048</v>
+        <v>14.85206</v>
       </c>
       <c r="F58">
-        <v>14.64848</v>
+        <v>14.91006</v>
       </c>
       <c r="G58">
         <v>0.415</v>
@@ -6171,37 +6171,37 @@
         <v>0.242</v>
       </c>
       <c r="M58">
-        <v>3.454111584000001</v>
+        <v>3.515792148000001</v>
       </c>
       <c r="N58">
-        <v>-3.212111584000001</v>
+        <v>-3.273792148000001</v>
       </c>
       <c r="O58">
-        <v>-0.5460589692800002</v>
+        <v>-0.5565446651600002</v>
       </c>
       <c r="P58">
-        <v>-2.666052614720001</v>
+        <v>-2.717247482840001</v>
       </c>
       <c r="Q58">
-        <v>-2.549052614720001</v>
+        <v>-2.600247482840001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3941329601930137</v>
+        <v>0.4022337267091304</v>
       </c>
       <c r="T58">
-        <v>1.247491755130925</v>
+        <v>1.276503191296761</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01191044324988431</v>
+        <v>0.01170148810514949</v>
       </c>
       <c r="W58">
-        <v>0.2329915174816773</v>
+        <v>0.2330407891048058</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.07006143088167238</v>
+        <v>0.0688322829714676</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3057937522746653</v>
+        <v>0.3076937522746653</v>
       </c>
       <c r="C59">
-        <v>0.8089621521012109</v>
+        <v>0.4363537604865222</v>
       </c>
       <c r="D59">
-        <v>15.30402215210121</v>
+        <v>15.19299376048652</v>
       </c>
       <c r="E59">
-        <v>14.85206</v>
+        <v>15.11364</v>
       </c>
       <c r="F59">
-        <v>14.91006</v>
+        <v>15.17164</v>
       </c>
       <c r="G59">
         <v>0.415</v>
@@ -6253,37 +6253,37 @@
         <v>0.242</v>
       </c>
       <c r="M59">
-        <v>3.515792148000001</v>
+        <v>3.577472712</v>
       </c>
       <c r="N59">
-        <v>-3.273792148000001</v>
+        <v>-3.335472712000001</v>
       </c>
       <c r="O59">
-        <v>-0.5565446651600002</v>
+        <v>-0.5670303610400002</v>
       </c>
       <c r="P59">
-        <v>-2.717247482840001</v>
+        <v>-2.76844235096</v>
       </c>
       <c r="Q59">
-        <v>-2.600247482840001</v>
+        <v>-2.65144235096</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4022337267091304</v>
+        <v>0.4107202440117287</v>
       </c>
       <c r="T59">
-        <v>1.276503191296761</v>
+        <v>1.306896124422874</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01170148810514949</v>
+        <v>0.01149973831023312</v>
       </c>
       <c r="W59">
-        <v>0.2330407891048058</v>
+        <v>0.233088361706447</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.0688322829714676</v>
+        <v>0.06764551947195951</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3076937522746653</v>
+        <v>0.3095937522746653</v>
       </c>
       <c r="C60">
-        <v>0.436353760486524</v>
+        <v>0.06534475431783981</v>
       </c>
       <c r="D60">
-        <v>15.19299376048652</v>
+        <v>15.08356475431784</v>
       </c>
       <c r="E60">
-        <v>15.11364</v>
+        <v>15.37522</v>
       </c>
       <c r="F60">
-        <v>15.17164</v>
+        <v>15.43322</v>
       </c>
       <c r="G60">
         <v>0.415</v>
@@ -6335,37 +6335,37 @@
         <v>0.242</v>
       </c>
       <c r="M60">
-        <v>3.577472712</v>
+        <v>3.639153276</v>
       </c>
       <c r="N60">
-        <v>-3.335472712</v>
+        <v>-3.397153276</v>
       </c>
       <c r="O60">
-        <v>-0.56703036104</v>
+        <v>-0.5775160569200001</v>
       </c>
       <c r="P60">
-        <v>-2.76844235096</v>
+        <v>-2.81963721908</v>
       </c>
       <c r="Q60">
-        <v>-2.65144235096</v>
+        <v>-2.70263721908</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4107202440117286</v>
+        <v>0.4196207377681123</v>
       </c>
       <c r="T60">
-        <v>1.306896124422874</v>
+        <v>1.3387716396527</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01149973831023313</v>
+        <v>0.01130482749141562</v>
       </c>
       <c r="W60">
-        <v>0.233088361706447</v>
+        <v>0.2331343216775242</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.06764551947195951</v>
+        <v>0.0664989852436213</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3095937522746653</v>
+        <v>0.3114937522746653</v>
       </c>
       <c r="C61">
-        <v>0.06534475431783981</v>
+        <v>-0.3040991784538161</v>
       </c>
       <c r="D61">
-        <v>15.08356475431784</v>
+        <v>14.97570082154619</v>
       </c>
       <c r="E61">
-        <v>15.37522</v>
+        <v>15.6368</v>
       </c>
       <c r="F61">
-        <v>15.43322</v>
+        <v>15.6948</v>
       </c>
       <c r="G61">
         <v>0.415</v>
@@ -6417,37 +6417,37 @@
         <v>0.242</v>
       </c>
       <c r="M61">
-        <v>3.639153276</v>
+        <v>3.70083384</v>
       </c>
       <c r="N61">
-        <v>-3.397153276</v>
+        <v>-3.45883384</v>
       </c>
       <c r="O61">
-        <v>-0.5775160569200001</v>
+        <v>-0.5880017528000001</v>
       </c>
       <c r="P61">
-        <v>-2.81963721908</v>
+        <v>-2.8708320872</v>
       </c>
       <c r="Q61">
-        <v>-2.70263721908</v>
+        <v>-2.7538320872</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4196207377681123</v>
+        <v>0.428966256212315</v>
       </c>
       <c r="T61">
-        <v>1.3387716396527</v>
+        <v>1.372240930644017</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01130482749141562</v>
+        <v>0.01111641369989202</v>
       </c>
       <c r="W61">
-        <v>0.2331343216775242</v>
+        <v>0.2331787496495655</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.0664989852436213</v>
+        <v>0.06539066882289424</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3114937522746653</v>
+        <v>0.3133937522746654</v>
       </c>
       <c r="C62">
-        <v>-0.3040991784538161</v>
+        <v>-0.6720113753719748</v>
       </c>
       <c r="D62">
-        <v>14.97570082154619</v>
+        <v>14.86936862462803</v>
       </c>
       <c r="E62">
-        <v>15.6368</v>
+        <v>15.89838</v>
       </c>
       <c r="F62">
-        <v>15.6948</v>
+        <v>15.95638</v>
       </c>
       <c r="G62">
         <v>0.415</v>
@@ -6499,37 +6499,37 @@
         <v>0.242</v>
       </c>
       <c r="M62">
-        <v>3.70083384</v>
+        <v>3.762514404</v>
       </c>
       <c r="N62">
-        <v>-3.45883384</v>
+        <v>-3.520514404</v>
       </c>
       <c r="O62">
-        <v>-0.5880017528000001</v>
+        <v>-0.5984874486800001</v>
       </c>
       <c r="P62">
-        <v>-2.8708320872</v>
+        <v>-2.92202695532</v>
       </c>
       <c r="Q62">
-        <v>-2.7538320872</v>
+        <v>-2.80502695532</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.428966256212315</v>
+        <v>0.4387910320126309</v>
       </c>
       <c r="T62">
-        <v>1.372240930644017</v>
+        <v>1.407426595532326</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01111641369989202</v>
+        <v>0.01093417740972986</v>
       </c>
       <c r="W62">
-        <v>0.2331787496495655</v>
+        <v>0.2332217209667857</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.06539066882289424</v>
+        <v>0.06431869064546969</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3133937522746654</v>
+        <v>0.3152937522746653</v>
       </c>
       <c r="C63">
-        <v>-0.6720113753719748</v>
+        <v>-1.038424233827255</v>
       </c>
       <c r="D63">
-        <v>14.86936862462803</v>
+        <v>14.76453576617275</v>
       </c>
       <c r="E63">
-        <v>15.89838</v>
+        <v>16.15996</v>
       </c>
       <c r="F63">
-        <v>15.95638</v>
+        <v>16.21796</v>
       </c>
       <c r="G63">
         <v>0.415</v>
@@ -6581,37 +6581,37 @@
         <v>0.242</v>
       </c>
       <c r="M63">
-        <v>3.762514404</v>
+        <v>3.824194968</v>
       </c>
       <c r="N63">
-        <v>-3.520514404</v>
+        <v>-3.582194968</v>
       </c>
       <c r="O63">
-        <v>-0.5984874486800001</v>
+        <v>-0.6089731445600002</v>
       </c>
       <c r="P63">
-        <v>-2.92202695532</v>
+        <v>-2.97322182344</v>
       </c>
       <c r="Q63">
-        <v>-2.80502695532</v>
+        <v>-2.85622182344</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4387910320126309</v>
+        <v>0.4491329012761212</v>
       </c>
       <c r="T63">
-        <v>1.407426595532326</v>
+        <v>1.444464137520018</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01093417740972986</v>
+        <v>0.01075781970957292</v>
       </c>
       <c r="W63">
-        <v>0.2332217209667857</v>
+        <v>0.2332633061124827</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.06431869064546969</v>
+        <v>0.06328129240925251</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3152937522746653</v>
+        <v>0.3171937522746653</v>
       </c>
       <c r="C64">
-        <v>-1.038424233827255</v>
+        <v>-1.403369243966978</v>
       </c>
       <c r="D64">
-        <v>14.76453576617275</v>
+        <v>14.66117075603302</v>
       </c>
       <c r="E64">
-        <v>16.15996</v>
+        <v>16.42154</v>
       </c>
       <c r="F64">
-        <v>16.21796</v>
+        <v>16.47954</v>
       </c>
       <c r="G64">
         <v>0.415</v>
@@ -6663,37 +6663,37 @@
         <v>0.242</v>
       </c>
       <c r="M64">
-        <v>3.824194968</v>
+        <v>3.885875532</v>
       </c>
       <c r="N64">
-        <v>-3.582194968</v>
+        <v>-3.643875532</v>
       </c>
       <c r="O64">
-        <v>-0.6089731445600002</v>
+        <v>-0.6194588404400001</v>
       </c>
       <c r="P64">
-        <v>-2.97322182344</v>
+        <v>-3.02441669156</v>
       </c>
       <c r="Q64">
-        <v>-2.85622182344</v>
+        <v>-2.90741669156</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4491329012761212</v>
+        <v>0.4600337904998001</v>
       </c>
       <c r="T64">
-        <v>1.444464137520018</v>
+        <v>1.483503708804343</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01075781970957292</v>
+        <v>0.01058706066656383</v>
       </c>
       <c r="W64">
-        <v>0.2332633061124827</v>
+        <v>0.2333035710948243</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.06328129240925251</v>
+        <v>0.06227682745037544</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3171937522746653</v>
+        <v>0.3190937522746653</v>
       </c>
       <c r="C65">
-        <v>-1.403369243966978</v>
+        <v>-1.766877020231936</v>
       </c>
       <c r="D65">
-        <v>14.66117075603302</v>
+        <v>14.55924297976807</v>
       </c>
       <c r="E65">
-        <v>16.42154</v>
+        <v>16.68312</v>
       </c>
       <c r="F65">
-        <v>16.47954</v>
+        <v>16.74112</v>
       </c>
       <c r="G65">
         <v>0.415</v>
@@ -6745,37 +6745,37 @@
         <v>0.242</v>
       </c>
       <c r="M65">
-        <v>3.885875532</v>
+        <v>3.947556096000001</v>
       </c>
       <c r="N65">
-        <v>-3.643875532</v>
+        <v>-3.705556096000001</v>
       </c>
       <c r="O65">
-        <v>-0.6194588404400001</v>
+        <v>-0.6299445363200002</v>
       </c>
       <c r="P65">
-        <v>-3.02441669156</v>
+        <v>-3.07561155968</v>
       </c>
       <c r="Q65">
-        <v>-2.90741669156</v>
+        <v>-2.95861155968</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4600337904998001</v>
+        <v>0.4715402846803501</v>
       </c>
       <c r="T65">
-        <v>1.483503708804343</v>
+        <v>1.52471214516002</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01058706066656383</v>
+        <v>0.01042163784364877</v>
       </c>
       <c r="W65">
-        <v>0.2333035710948243</v>
+        <v>0.2333425777964676</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.06227682745037544</v>
+        <v>0.06130375202146332</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3190937522746653</v>
+        <v>0.3209937522746653</v>
       </c>
       <c r="C66">
-        <v>-1.766877020231936</v>
+        <v>-2.128977331586785</v>
       </c>
       <c r="D66">
-        <v>14.55924297976807</v>
+        <v>14.45872266841322</v>
       </c>
       <c r="E66">
-        <v>16.68312</v>
+        <v>16.9447</v>
       </c>
       <c r="F66">
-        <v>16.74112</v>
+        <v>17.0027</v>
       </c>
       <c r="G66">
         <v>0.415</v>
@@ -6827,37 +6827,37 @@
         <v>0.242</v>
       </c>
       <c r="M66">
-        <v>3.947556096000001</v>
+        <v>4.00923666</v>
       </c>
       <c r="N66">
-        <v>-3.705556096000001</v>
+        <v>-3.76723666</v>
       </c>
       <c r="O66">
-        <v>-0.6299445363200002</v>
+        <v>-0.6404302322000001</v>
       </c>
       <c r="P66">
-        <v>-3.07561155968</v>
+        <v>-3.1268064278</v>
       </c>
       <c r="Q66">
-        <v>-2.95861155968</v>
+        <v>-3.0098064278</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4715402846803501</v>
+        <v>0.4837042928140744</v>
       </c>
       <c r="T66">
-        <v>1.52471214516002</v>
+        <v>1.568275349307449</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01042163784364877</v>
+        <v>0.01026130495374648</v>
       </c>
       <c r="W66">
-        <v>0.2333425777964676</v>
+        <v>0.2333803842919066</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.06130375202146332</v>
+        <v>0.06036061737497933</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3209937522746653</v>
+        <v>0.3228937522746653</v>
       </c>
       <c r="C67">
-        <v>-2.128977331586785</v>
+        <v>-2.489699130506724</v>
       </c>
       <c r="D67">
-        <v>14.45872266841322</v>
+        <v>14.35958086949328</v>
       </c>
       <c r="E67">
-        <v>16.9447</v>
+        <v>17.20628</v>
       </c>
       <c r="F67">
-        <v>17.0027</v>
+        <v>17.26428</v>
       </c>
       <c r="G67">
         <v>0.415</v>
@@ -6909,37 +6909,37 @@
         <v>0.242</v>
       </c>
       <c r="M67">
-        <v>4.00923666</v>
+        <v>4.070917224</v>
       </c>
       <c r="N67">
-        <v>-3.76723666</v>
+        <v>-3.828917224</v>
       </c>
       <c r="O67">
-        <v>-0.6404302322000001</v>
+        <v>-0.6509159280800001</v>
       </c>
       <c r="P67">
-        <v>-3.1268064278</v>
+        <v>-3.178001295920001</v>
       </c>
       <c r="Q67">
-        <v>-3.0098064278</v>
+        <v>-3.061001295920001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4837042928140744</v>
+        <v>0.4965838308380178</v>
       </c>
       <c r="T67">
-        <v>1.568275349307449</v>
+        <v>1.614401094875315</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01026130495374648</v>
+        <v>0.01010583063626547</v>
       </c>
       <c r="W67">
-        <v>0.2333803842919066</v>
+        <v>0.2334170451359686</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.06036061737497933</v>
+        <v>0.0594460625662675</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3228937522746653</v>
+        <v>0.3247937522746653</v>
       </c>
       <c r="C68">
-        <v>-2.489699130506724</v>
+        <v>-2.849070580779692</v>
       </c>
       <c r="D68">
-        <v>14.35958086949328</v>
+        <v>14.26178941922031</v>
       </c>
       <c r="E68">
-        <v>17.20628</v>
+        <v>17.46786</v>
       </c>
       <c r="F68">
-        <v>17.26428</v>
+        <v>17.52586</v>
       </c>
       <c r="G68">
         <v>0.415</v>
@@ -6991,37 +6991,37 @@
         <v>0.242</v>
       </c>
       <c r="M68">
-        <v>4.070917224</v>
+        <v>4.132597788000001</v>
       </c>
       <c r="N68">
-        <v>-3.828917224</v>
+        <v>-3.890597788000001</v>
       </c>
       <c r="O68">
-        <v>-0.6509159280800001</v>
+        <v>-0.6614016239600002</v>
       </c>
       <c r="P68">
-        <v>-3.178001295920001</v>
+        <v>-3.229196164040001</v>
       </c>
       <c r="Q68">
-        <v>-3.061001295920001</v>
+        <v>-3.112196164040001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4965838308380178</v>
+        <v>0.5102439469240183</v>
       </c>
       <c r="T68">
-        <v>1.614401094875315</v>
+        <v>1.663322340174567</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01010583063626547</v>
+        <v>0.009954997343186884</v>
       </c>
       <c r="W68">
-        <v>0.2334170451359686</v>
+        <v>0.2334526116264765</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.0594460625662675</v>
+        <v>0.05855880790109935</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3247937522746653</v>
+        <v>0.3266937522746653</v>
       </c>
       <c r="C69">
-        <v>-2.849070580779692</v>
+        <v>-3.207119084180306</v>
       </c>
       <c r="D69">
-        <v>14.26178941922031</v>
+        <v>14.1653209158197</v>
       </c>
       <c r="E69">
-        <v>17.46786</v>
+        <v>17.72944</v>
       </c>
       <c r="F69">
-        <v>17.52586</v>
+        <v>17.78744</v>
       </c>
       <c r="G69">
         <v>0.415</v>
@@ -7073,37 +7073,37 @@
         <v>0.242</v>
       </c>
       <c r="M69">
-        <v>4.132597788000001</v>
+        <v>4.194278352000001</v>
       </c>
       <c r="N69">
-        <v>-3.890597788000001</v>
+        <v>-3.952278352000001</v>
       </c>
       <c r="O69">
-        <v>-0.6614016239600002</v>
+        <v>-0.6718873198400003</v>
       </c>
       <c r="P69">
-        <v>-3.229196164040001</v>
+        <v>-3.280391032160001</v>
       </c>
       <c r="Q69">
-        <v>-3.112196164040001</v>
+        <v>-3.163391032160001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5102439469240183</v>
+        <v>0.5247578202653939</v>
       </c>
       <c r="T69">
-        <v>1.663322340174567</v>
+        <v>1.715301163305022</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.009954997343186884</v>
+        <v>0.009808600323434134</v>
       </c>
       <c r="W69">
-        <v>0.2334526116264765</v>
+        <v>0.2334871320437343</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.05855880790109935</v>
+        <v>0.0576976489613773</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3266937522746653</v>
+        <v>0.3285937522746653</v>
       </c>
       <c r="C70">
-        <v>-3.207119084180306</v>
+        <v>-3.563871306068419</v>
       </c>
       <c r="D70">
-        <v>14.1653209158197</v>
+        <v>14.07014869393158</v>
       </c>
       <c r="E70">
-        <v>17.72944</v>
+        <v>17.99102</v>
       </c>
       <c r="F70">
-        <v>17.78744</v>
+        <v>18.04902</v>
       </c>
       <c r="G70">
         <v>0.415</v>
@@ -7155,37 +7155,37 @@
         <v>0.242</v>
       </c>
       <c r="M70">
-        <v>4.194278352000001</v>
+        <v>4.255958916000001</v>
       </c>
       <c r="N70">
-        <v>-3.952278352000001</v>
+        <v>-4.013958916000001</v>
       </c>
       <c r="O70">
-        <v>-0.6718873198400003</v>
+        <v>-0.6823730157200002</v>
       </c>
       <c r="P70">
-        <v>-3.280391032160001</v>
+        <v>-3.331585900280001</v>
       </c>
       <c r="Q70">
-        <v>-3.163391032160001</v>
+        <v>-3.214585900280001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5247578202653939</v>
+        <v>0.5402080725320195</v>
       </c>
       <c r="T70">
-        <v>1.715301163305022</v>
+        <v>1.770633458895507</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.009808600323434134</v>
+        <v>0.009666446695558278</v>
       </c>
       <c r="W70">
-        <v>0.2334871320437343</v>
+        <v>0.2335206518691874</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.0576976489613773</v>
+        <v>0.0568614511503428</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3285937522746653</v>
+        <v>0.3304937522746653</v>
       </c>
       <c r="C71">
-        <v>-3.563871306068419</v>
+        <v>-3.919353199962732</v>
       </c>
       <c r="D71">
-        <v>14.07014869393158</v>
+        <v>13.97624680003727</v>
       </c>
       <c r="E71">
-        <v>17.99102</v>
+        <v>18.2526</v>
       </c>
       <c r="F71">
-        <v>18.04902</v>
+        <v>18.3106</v>
       </c>
       <c r="G71">
         <v>0.415</v>
@@ -7237,37 +7237,37 @@
         <v>0.242</v>
       </c>
       <c r="M71">
-        <v>4.255958916000001</v>
+        <v>4.31763948</v>
       </c>
       <c r="N71">
-        <v>-4.013958916000001</v>
+        <v>-4.07563948</v>
       </c>
       <c r="O71">
-        <v>-0.6823730157200002</v>
+        <v>-0.6928587116000001</v>
       </c>
       <c r="P71">
-        <v>-3.331585900280001</v>
+        <v>-3.3827807684</v>
       </c>
       <c r="Q71">
-        <v>-3.214585900280001</v>
+        <v>-3.2657807684</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5402080725320195</v>
+        <v>0.5566883416164201</v>
       </c>
       <c r="T71">
-        <v>1.770633458895507</v>
+        <v>1.829654574192024</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.009666446695558278</v>
+        <v>0.009528354599907448</v>
       </c>
       <c r="W71">
-        <v>0.2335206518691874</v>
+        <v>0.2335532139853418</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.0568614511503428</v>
+        <v>0.05604914470533795</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3304937522746653</v>
+        <v>0.3323937522746653</v>
       </c>
       <c r="C72">
-        <v>-3.919353199962732</v>
+        <v>-4.273590031136857</v>
       </c>
       <c r="D72">
-        <v>13.97624680003727</v>
+        <v>13.88358996886315</v>
       </c>
       <c r="E72">
-        <v>18.2526</v>
+        <v>18.51418</v>
       </c>
       <c r="F72">
-        <v>18.3106</v>
+        <v>18.57218</v>
       </c>
       <c r="G72">
         <v>0.415</v>
@@ -7319,37 +7319,37 @@
         <v>0.242</v>
       </c>
       <c r="M72">
-        <v>4.31763948</v>
+        <v>4.379320044000001</v>
       </c>
       <c r="N72">
-        <v>-4.07563948</v>
+        <v>-4.137320044000001</v>
       </c>
       <c r="O72">
-        <v>-0.6928587116000001</v>
+        <v>-0.7033444074800002</v>
       </c>
       <c r="P72">
-        <v>-3.3827807684</v>
+        <v>-3.43397563652</v>
       </c>
       <c r="Q72">
-        <v>-3.2657807684</v>
+        <v>-3.31697563652</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5566883416164201</v>
+        <v>0.5743051809825037</v>
       </c>
       <c r="T72">
-        <v>1.829654574192024</v>
+        <v>1.892746111233128</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.009528354599907448</v>
+        <v>0.009394152422443961</v>
       </c>
       <c r="W72">
-        <v>0.2335532139853418</v>
+        <v>0.2335848588587877</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.05604914470533795</v>
+        <v>0.05525972013202329</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3323937522746653</v>
+        <v>0.3342937522746653</v>
       </c>
       <c r="C73">
-        <v>-4.273590031136846</v>
+        <v>-4.626606399282965</v>
       </c>
       <c r="D73">
-        <v>13.88358996886315</v>
+        <v>13.79215360071704</v>
       </c>
       <c r="E73">
-        <v>18.51418</v>
+        <v>18.77576</v>
       </c>
       <c r="F73">
-        <v>18.57218</v>
+        <v>18.83376</v>
       </c>
       <c r="G73">
         <v>0.415</v>
@@ -7401,37 +7401,37 @@
         <v>0.242</v>
       </c>
       <c r="M73">
-        <v>4.379320044</v>
+        <v>4.441000608</v>
       </c>
       <c r="N73">
-        <v>-4.137320044</v>
+        <v>-4.199000608</v>
       </c>
       <c r="O73">
-        <v>-0.70334440748</v>
+        <v>-0.7138301033600001</v>
       </c>
       <c r="P73">
-        <v>-3.43397563652</v>
+        <v>-3.48517050464</v>
       </c>
       <c r="Q73">
-        <v>-3.31697563652</v>
+        <v>-3.36817050464</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5743051809825035</v>
+        <v>0.5931803660175929</v>
       </c>
       <c r="T73">
-        <v>1.892746111233127</v>
+        <v>1.960344186634311</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.009394152422443963</v>
+        <v>0.009263678083243352</v>
       </c>
       <c r="W73">
-        <v>0.2335848588587877</v>
+        <v>0.2336156247079712</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.05525972013202329</v>
+        <v>0.05449222401907849</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3342937522746653</v>
+        <v>0.3361937522746653</v>
       </c>
       <c r="C74">
-        <v>-4.626606399282965</v>
+        <v>-4.978426260285815</v>
       </c>
       <c r="D74">
-        <v>13.79215360071704</v>
+        <v>13.70191373971419</v>
       </c>
       <c r="E74">
-        <v>18.77576</v>
+        <v>19.03734</v>
       </c>
       <c r="F74">
-        <v>18.83376</v>
+        <v>19.09534</v>
       </c>
       <c r="G74">
         <v>0.415</v>
@@ -7483,37 +7483,37 @@
         <v>0.242</v>
       </c>
       <c r="M74">
-        <v>4.441000608</v>
+        <v>4.502681172</v>
       </c>
       <c r="N74">
-        <v>-4.199000608</v>
+        <v>-4.260681172</v>
       </c>
       <c r="O74">
-        <v>-0.7138301033600001</v>
+        <v>-0.72431579924</v>
       </c>
       <c r="P74">
-        <v>-3.48517050464</v>
+        <v>-3.53636537276</v>
       </c>
       <c r="Q74">
-        <v>-3.36817050464</v>
+        <v>-3.41936537276</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5931803660175929</v>
+        <v>0.6134537129071334</v>
       </c>
       <c r="T74">
-        <v>1.960344186634311</v>
+        <v>2.032949526880026</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.009263678083243352</v>
+        <v>0.009136778383472896</v>
       </c>
       <c r="W74">
-        <v>0.2336156247079712</v>
+        <v>0.2336455476571771</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.05449222401907849</v>
+        <v>0.05374575519689939</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3361937522746653</v>
+        <v>0.3380937522746653</v>
       </c>
       <c r="C75">
-        <v>-4.978426260285815</v>
+        <v>-5.329072947147441</v>
       </c>
       <c r="D75">
-        <v>13.70191373971419</v>
+        <v>13.61284705285256</v>
       </c>
       <c r="E75">
-        <v>19.03734</v>
+        <v>19.29892</v>
       </c>
       <c r="F75">
-        <v>19.09534</v>
+        <v>19.35692</v>
       </c>
       <c r="G75">
         <v>0.415</v>
@@ -7565,37 +7565,37 @@
         <v>0.242</v>
       </c>
       <c r="M75">
-        <v>4.502681172</v>
+        <v>4.564361736</v>
       </c>
       <c r="N75">
-        <v>-4.260681172</v>
+        <v>-4.322361736</v>
       </c>
       <c r="O75">
-        <v>-0.72431579924</v>
+        <v>-0.7348014951200001</v>
       </c>
       <c r="P75">
-        <v>-3.53636537276</v>
+        <v>-3.58756024088</v>
       </c>
       <c r="Q75">
-        <v>-3.41936537276</v>
+        <v>-3.47056024088</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6134537129071334</v>
+        <v>0.6352865480189461</v>
       </c>
       <c r="T75">
-        <v>2.032949526880026</v>
+        <v>2.111139893298488</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.009136778383472896</v>
+        <v>0.009013308405317857</v>
       </c>
       <c r="W75">
-        <v>0.2336455476571771</v>
+        <v>0.233674661878026</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.05374575519689939</v>
+        <v>0.05301946120775214</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3380937522746653</v>
+        <v>0.3399937522746653</v>
       </c>
       <c r="C76">
-        <v>-5.329072947147441</v>
+        <v>-5.678569190101074</v>
       </c>
       <c r="D76">
-        <v>13.61284705285256</v>
+        <v>13.52493080989893</v>
       </c>
       <c r="E76">
-        <v>19.29892</v>
+        <v>19.5605</v>
       </c>
       <c r="F76">
-        <v>19.35692</v>
+        <v>19.6185</v>
       </c>
       <c r="G76">
         <v>0.415</v>
@@ -7647,37 +7647,37 @@
         <v>0.242</v>
       </c>
       <c r="M76">
-        <v>4.564361736</v>
+        <v>4.626042300000001</v>
       </c>
       <c r="N76">
-        <v>-4.322361736</v>
+        <v>-4.384042300000001</v>
       </c>
       <c r="O76">
-        <v>-0.7348014951200001</v>
+        <v>-0.7452871910000002</v>
       </c>
       <c r="P76">
-        <v>-3.58756024088</v>
+        <v>-3.638755109000001</v>
       </c>
       <c r="Q76">
-        <v>-3.47056024088</v>
+        <v>-3.521755109000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6352865480189461</v>
+        <v>0.6588660099397041</v>
       </c>
       <c r="T76">
-        <v>2.111139893298488</v>
+        <v>2.195585489030428</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.009013308405317857</v>
+        <v>0.008893130959913616</v>
       </c>
       <c r="W76">
-        <v>0.233674661878026</v>
+        <v>0.2337029997196524</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.05301946120775214</v>
+        <v>0.05231253505831535</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3399937522746653</v>
+        <v>0.3418937522746653</v>
       </c>
       <c r="C77">
-        <v>-5.678569190101074</v>
+        <v>-6.026937135950638</v>
       </c>
       <c r="D77">
-        <v>13.52493080989893</v>
+        <v>13.43814286404936</v>
       </c>
       <c r="E77">
-        <v>19.5605</v>
+        <v>19.82208</v>
       </c>
       <c r="F77">
-        <v>19.6185</v>
+        <v>19.88008</v>
       </c>
       <c r="G77">
         <v>0.415</v>
@@ -7729,37 +7729,37 @@
         <v>0.242</v>
       </c>
       <c r="M77">
-        <v>4.626042300000001</v>
+        <v>4.687722864</v>
       </c>
       <c r="N77">
-        <v>-4.384042300000001</v>
+        <v>-4.445722864</v>
       </c>
       <c r="O77">
-        <v>-0.7452871910000002</v>
+        <v>-0.7557728868800001</v>
       </c>
       <c r="P77">
-        <v>-3.638755109000001</v>
+        <v>-3.68994997712</v>
       </c>
       <c r="Q77">
-        <v>-3.521755109000001</v>
+        <v>-3.57294997712</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6588660099397041</v>
+        <v>0.6844104270205251</v>
       </c>
       <c r="T77">
-        <v>2.195585489030428</v>
+        <v>2.287068217740029</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.008893130959913616</v>
+        <v>0.008776116078862122</v>
       </c>
       <c r="W77">
-        <v>0.2337029997196524</v>
+        <v>0.2337305918286043</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.05231253505831535</v>
+        <v>0.0516242122286007</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3418937522746653</v>
+        <v>0.3437937522746653</v>
       </c>
       <c r="C78">
-        <v>-6.026937135950638</v>
+        <v>-6.374198366670402</v>
       </c>
       <c r="D78">
-        <v>13.43814286404936</v>
+        <v>13.3524616333296</v>
       </c>
       <c r="E78">
-        <v>19.82208</v>
+        <v>20.08366</v>
       </c>
       <c r="F78">
-        <v>19.88008</v>
+        <v>20.14166</v>
       </c>
       <c r="G78">
         <v>0.415</v>
@@ -7811,37 +7811,37 @@
         <v>0.242</v>
       </c>
       <c r="M78">
-        <v>4.687722864</v>
+        <v>4.749403428000001</v>
       </c>
       <c r="N78">
-        <v>-4.445722864</v>
+        <v>-4.507403428000001</v>
       </c>
       <c r="O78">
-        <v>-0.7557728868800001</v>
+        <v>-0.7662585827600001</v>
       </c>
       <c r="P78">
-        <v>-3.68994997712</v>
+        <v>-3.741144845240001</v>
       </c>
       <c r="Q78">
-        <v>-3.57294997712</v>
+        <v>-3.624144845240001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.6844104270205251</v>
+        <v>0.7121760977605479</v>
       </c>
       <c r="T78">
-        <v>2.287068217740029</v>
+        <v>2.386505966337422</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.008776116078862122</v>
+        <v>0.008662140545370406</v>
       </c>
       <c r="W78">
-        <v>0.2337305918286043</v>
+        <v>0.2337574672594017</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0516242122286007</v>
+        <v>0.05095376791394357</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3437937522746653</v>
+        <v>0.3456937522746653</v>
       </c>
       <c r="C79">
-        <v>-6.374198366670402</v>
+        <v>-6.720373917297579</v>
       </c>
       <c r="D79">
-        <v>13.3524616333296</v>
+        <v>13.26786608270242</v>
       </c>
       <c r="E79">
-        <v>20.08366</v>
+        <v>20.34524</v>
       </c>
       <c r="F79">
-        <v>20.14166</v>
+        <v>20.40324</v>
       </c>
       <c r="G79">
         <v>0.415</v>
@@ -7893,37 +7893,37 @@
         <v>0.242</v>
       </c>
       <c r="M79">
-        <v>4.749403428000001</v>
+        <v>4.811083992</v>
       </c>
       <c r="N79">
-        <v>-4.507403428000001</v>
+        <v>-4.569083992</v>
       </c>
       <c r="O79">
-        <v>-0.7662585827600001</v>
+        <v>-0.7767442786400002</v>
       </c>
       <c r="P79">
-        <v>-3.741144845240001</v>
+        <v>-3.79233971336</v>
       </c>
       <c r="Q79">
-        <v>-3.624144845240001</v>
+        <v>-3.67533971336</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.7121760977605479</v>
+        <v>0.7424659203860274</v>
       </c>
       <c r="T79">
-        <v>2.386505966337422</v>
+        <v>2.49498351026185</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.008662140545370406</v>
+        <v>0.008551087461455402</v>
       </c>
       <c r="W79">
-        <v>0.2337574672594017</v>
+        <v>0.2337836535765888</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.05095376791394357</v>
+        <v>0.05030051447914941</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3456937522746653</v>
+        <v>0.3475937522746653</v>
       </c>
       <c r="C80">
-        <v>-6.720373917297579</v>
+        <v>-7.065484293149074</v>
       </c>
       <c r="D80">
-        <v>13.26786608270242</v>
+        <v>13.18433570685093</v>
       </c>
       <c r="E80">
-        <v>20.34524</v>
+        <v>20.60682</v>
       </c>
       <c r="F80">
-        <v>20.40324</v>
+        <v>20.66482</v>
       </c>
       <c r="G80">
         <v>0.415</v>
@@ -7975,37 +7975,37 @@
         <v>0.242</v>
       </c>
       <c r="M80">
-        <v>4.811083992</v>
+        <v>4.872764556000001</v>
       </c>
       <c r="N80">
-        <v>-4.569083992</v>
+        <v>-4.630764556000001</v>
       </c>
       <c r="O80">
-        <v>-0.7767442786400002</v>
+        <v>-0.7872299745200002</v>
       </c>
       <c r="P80">
-        <v>-3.79233971336</v>
+        <v>-3.843534581480001</v>
       </c>
       <c r="Q80">
-        <v>-3.67533971336</v>
+        <v>-3.726534581480001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7424659203860274</v>
+        <v>0.7756404880234574</v>
       </c>
       <c r="T80">
-        <v>2.49498351026185</v>
+        <v>2.613792248845748</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.008551087461455402</v>
+        <v>0.008442845848019256</v>
       </c>
       <c r="W80">
-        <v>0.2337836535765888</v>
+        <v>0.2338091769490371</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.05030051447914941</v>
+        <v>0.04966379910599561</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3475937522746653</v>
+        <v>0.3494937522746653</v>
       </c>
       <c r="C81">
-        <v>-7.065484293149074</v>
+        <v>-7.409549486391903</v>
       </c>
       <c r="D81">
-        <v>13.18433570685093</v>
+        <v>13.1018505136081</v>
       </c>
       <c r="E81">
-        <v>20.60682</v>
+        <v>20.8684</v>
       </c>
       <c r="F81">
-        <v>20.66482</v>
+        <v>20.9264</v>
       </c>
       <c r="G81">
         <v>0.415</v>
@@ -8057,37 +8057,37 @@
         <v>0.242</v>
       </c>
       <c r="M81">
-        <v>4.872764556000001</v>
+        <v>4.93444512</v>
       </c>
       <c r="N81">
-        <v>-4.630764556000001</v>
+        <v>-4.69244512</v>
       </c>
       <c r="O81">
-        <v>-0.7872299745200002</v>
+        <v>-0.7977156704000001</v>
       </c>
       <c r="P81">
-        <v>-3.843534581480001</v>
+        <v>-3.8947294496</v>
       </c>
       <c r="Q81">
-        <v>-3.726534581480001</v>
+        <v>-3.7777294496</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7756404880234574</v>
+        <v>0.8121325124246302</v>
       </c>
       <c r="T81">
-        <v>2.613792248845748</v>
+        <v>2.744481861288036</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.008442845848019256</v>
+        <v>0.008337310274919015</v>
       </c>
       <c r="W81">
-        <v>0.2338091769490371</v>
+        <v>0.2338340622371741</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.04966379910599561</v>
+        <v>0.04904300161717068</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3494937522746653</v>
+        <v>0.3513937522746653</v>
       </c>
       <c r="C82">
-        <v>-7.409549486391903</v>
+        <v>-7.752588991995545</v>
       </c>
       <c r="D82">
-        <v>13.1018505136081</v>
+        <v>13.02039100800446</v>
       </c>
       <c r="E82">
-        <v>20.8684</v>
+        <v>21.12998</v>
       </c>
       <c r="F82">
-        <v>20.9264</v>
+        <v>21.18798</v>
       </c>
       <c r="G82">
         <v>0.415</v>
@@ -8139,37 +8139,37 @@
         <v>0.242</v>
       </c>
       <c r="M82">
-        <v>4.93444512</v>
+        <v>4.996125684000001</v>
       </c>
       <c r="N82">
-        <v>-4.69244512</v>
+        <v>-4.754125684000001</v>
       </c>
       <c r="O82">
-        <v>-0.7977156704000001</v>
+        <v>-0.8082013662800002</v>
       </c>
       <c r="P82">
-        <v>-3.8947294496</v>
+        <v>-3.945924317720001</v>
       </c>
       <c r="Q82">
-        <v>-3.7777294496</v>
+        <v>-3.828924317720001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.8121325124246302</v>
+        <v>0.8524658025522424</v>
       </c>
       <c r="T82">
-        <v>2.744481861288036</v>
+        <v>2.888928275040037</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.008337310274919015</v>
+        <v>0.008234380518438535</v>
       </c>
       <c r="W82">
-        <v>0.2338340622371741</v>
+        <v>0.2338583330737522</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.04904300161717068</v>
+        <v>0.04843753246140314</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3513937522746653</v>
+        <v>0.3532937522746653</v>
       </c>
       <c r="C83">
-        <v>-7.752588991995545</v>
+        <v>-8.09462182309278</v>
       </c>
       <c r="D83">
-        <v>13.02039100800446</v>
+        <v>12.93993817690722</v>
       </c>
       <c r="E83">
-        <v>21.12998</v>
+        <v>21.39156</v>
       </c>
       <c r="F83">
-        <v>21.18798</v>
+        <v>21.44956</v>
       </c>
       <c r="G83">
         <v>0.415</v>
@@ -8221,37 +8221,37 @@
         <v>0.242</v>
       </c>
       <c r="M83">
-        <v>4.996125684000001</v>
+        <v>5.057806248</v>
       </c>
       <c r="N83">
-        <v>-4.754125684000001</v>
+        <v>-4.815806248</v>
       </c>
       <c r="O83">
-        <v>-0.8082013662800002</v>
+        <v>-0.8186870621600001</v>
       </c>
       <c r="P83">
-        <v>-3.945924317720001</v>
+        <v>-3.99711918584</v>
       </c>
       <c r="Q83">
-        <v>-3.828924317720001</v>
+        <v>-3.88011918584</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8524658025522424</v>
+        <v>0.8972805693607003</v>
       </c>
       <c r="T83">
-        <v>2.888928275040037</v>
+        <v>3.04942429032004</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.008234380518438535</v>
+        <v>0.008133961243823431</v>
       </c>
       <c r="W83">
-        <v>0.2338583330737522</v>
+        <v>0.2338820119387064</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.04843753246140314</v>
+        <v>0.04784683084602015</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3532937522746653</v>
+        <v>0.3551937522746653</v>
       </c>
       <c r="C84">
-        <v>-8.09462182309278</v>
+        <v>-8.435666525774618</v>
       </c>
       <c r="D84">
-        <v>12.93993817690722</v>
+        <v>12.86047347422539</v>
       </c>
       <c r="E84">
-        <v>21.39156</v>
+        <v>21.65314</v>
       </c>
       <c r="F84">
-        <v>21.44956</v>
+        <v>21.71114</v>
       </c>
       <c r="G84">
         <v>0.415</v>
@@ -8303,37 +8303,37 @@
         <v>0.242</v>
       </c>
       <c r="M84">
-        <v>5.057806248</v>
+        <v>5.119486812000001</v>
       </c>
       <c r="N84">
-        <v>-4.815806248</v>
+        <v>-4.877486812000001</v>
       </c>
       <c r="O84">
-        <v>-0.8186870621600001</v>
+        <v>-0.8291727580400002</v>
       </c>
       <c r="P84">
-        <v>-3.99711918584</v>
+        <v>-4.04831405396</v>
       </c>
       <c r="Q84">
-        <v>-3.88011918584</v>
+        <v>-3.93131405396</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.8972805693607003</v>
+        <v>0.9473676616760358</v>
       </c>
       <c r="T84">
-        <v>3.04942429032004</v>
+        <v>3.228802189750631</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.008133961243823431</v>
+        <v>0.008035961710765318</v>
       </c>
       <c r="W84">
-        <v>0.2338820119387064</v>
+        <v>0.2339051202286015</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.04784683084602015</v>
+        <v>0.04727036300450183</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3551937522746653</v>
+        <v>0.3570937522746653</v>
       </c>
       <c r="C85">
-        <v>-8.435666525774618</v>
+        <v>-8.775741193343366</v>
       </c>
       <c r="D85">
-        <v>12.86047347422539</v>
+        <v>12.78197880665664</v>
       </c>
       <c r="E85">
-        <v>21.65314</v>
+        <v>21.91472</v>
       </c>
       <c r="F85">
-        <v>21.71114</v>
+        <v>21.97272</v>
       </c>
       <c r="G85">
         <v>0.415</v>
@@ -8385,37 +8385,37 @@
         <v>0.242</v>
       </c>
       <c r="M85">
-        <v>5.119486812000001</v>
+        <v>5.181167376000001</v>
       </c>
       <c r="N85">
-        <v>-4.877486812000001</v>
+        <v>-4.939167376000001</v>
       </c>
       <c r="O85">
-        <v>-0.8291727580400002</v>
+        <v>-0.8396584539200003</v>
       </c>
       <c r="P85">
-        <v>-4.04831405396</v>
+        <v>-4.099508922080001</v>
       </c>
       <c r="Q85">
-        <v>-3.93131405396</v>
+        <v>-3.982508922080001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.9473676616760358</v>
+        <v>1.003715640530788</v>
       </c>
       <c r="T85">
-        <v>3.228802189750631</v>
+        <v>3.430602326610046</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.008035961710765318</v>
+        <v>0.00794029549992287</v>
       </c>
       <c r="W85">
-        <v>0.2339051202286015</v>
+        <v>0.2339276783211182</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.04727036300450183</v>
+        <v>0.04670762058778155</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3570937522746653</v>
+        <v>0.3589937522746653</v>
       </c>
       <c r="C86">
-        <v>-8.775741193343359</v>
+        <v>-9.11486348004693</v>
       </c>
       <c r="D86">
-        <v>12.78197880665664</v>
+        <v>12.70443651995307</v>
       </c>
       <c r="E86">
-        <v>21.91472</v>
+        <v>22.1763</v>
       </c>
       <c r="F86">
-        <v>21.97272</v>
+        <v>22.2343</v>
       </c>
       <c r="G86">
         <v>0.415</v>
@@ -8467,37 +8467,37 @@
         <v>0.242</v>
       </c>
       <c r="M86">
-        <v>5.181167376</v>
+        <v>5.242847940000001</v>
       </c>
       <c r="N86">
-        <v>-4.939167376</v>
+        <v>-5.000847940000001</v>
       </c>
       <c r="O86">
-        <v>-0.8396584539200002</v>
+        <v>-0.8501441498000002</v>
       </c>
       <c r="P86">
-        <v>-4.09950892208</v>
+        <v>-4.150703790200001</v>
       </c>
       <c r="Q86">
-        <v>-3.98250892208</v>
+        <v>-4.033703790200001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.003715640530787</v>
+        <v>1.06757668323284</v>
       </c>
       <c r="T86">
-        <v>3.430602326610043</v>
+        <v>3.659309148384046</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.007940295499922872</v>
+        <v>0.007846880258747309</v>
       </c>
       <c r="W86">
-        <v>0.2339276783211182</v>
+        <v>0.2339497056349874</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.04670762058778155</v>
+        <v>0.04615811916910184</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3589937522746653</v>
+        <v>0.3608937522746654</v>
       </c>
       <c r="C87">
-        <v>-9.11486348004693</v>
+        <v>-9.45305061431619</v>
       </c>
       <c r="D87">
-        <v>12.70443651995307</v>
+        <v>12.62782938568381</v>
       </c>
       <c r="E87">
-        <v>22.1763</v>
+        <v>22.43788</v>
       </c>
       <c r="F87">
-        <v>22.2343</v>
+        <v>22.49588</v>
       </c>
       <c r="G87">
         <v>0.415</v>
@@ -8549,37 +8549,37 @@
         <v>0.242</v>
       </c>
       <c r="M87">
-        <v>5.242847940000001</v>
+        <v>5.304528504</v>
       </c>
       <c r="N87">
-        <v>-5.000847940000001</v>
+        <v>-5.062528504</v>
       </c>
       <c r="O87">
-        <v>-0.8501441498000002</v>
+        <v>-0.8606298456800001</v>
       </c>
       <c r="P87">
-        <v>-4.150703790200001</v>
+        <v>-4.20189865832</v>
       </c>
       <c r="Q87">
-        <v>-4.033703790200001</v>
+        <v>-4.08489865832</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.06757668323284</v>
+        <v>1.140560732035186</v>
       </c>
       <c r="T87">
-        <v>3.659309148384046</v>
+        <v>3.920688373268621</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.007846880258747309</v>
+        <v>0.007755637465040945</v>
       </c>
       <c r="W87">
-        <v>0.2339497056349874</v>
+        <v>0.2339712206857434</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.04615811916910184</v>
+        <v>0.04562139685318201</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3608937522746654</v>
+        <v>0.3627937522746653</v>
       </c>
       <c r="C88">
-        <v>-9.45305061431619</v>
+        <v>-9.790319411526333</v>
       </c>
       <c r="D88">
-        <v>12.62782938568381</v>
+        <v>12.55214058847367</v>
       </c>
       <c r="E88">
-        <v>22.43788</v>
+        <v>22.69946</v>
       </c>
       <c r="F88">
-        <v>22.49588</v>
+        <v>22.75746</v>
       </c>
       <c r="G88">
         <v>0.415</v>
@@ -8631,37 +8631,37 @@
         <v>0.242</v>
       </c>
       <c r="M88">
-        <v>5.304528504</v>
+        <v>5.366209068000001</v>
       </c>
       <c r="N88">
-        <v>-5.062528504</v>
+        <v>-5.124209068000001</v>
       </c>
       <c r="O88">
-        <v>-0.8606298456800001</v>
+        <v>-0.8711155415600002</v>
       </c>
       <c r="P88">
-        <v>-4.20189865832</v>
+        <v>-4.253093526440001</v>
       </c>
       <c r="Q88">
-        <v>-4.08489865832</v>
+        <v>-4.136093526440001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.140560732035186</v>
+        <v>1.224773096037892</v>
       </c>
       <c r="T88">
-        <v>3.920688373268621</v>
+        <v>4.222279786596976</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.007755637465040945</v>
+        <v>0.007666492206822083</v>
       </c>
       <c r="W88">
-        <v>0.2339712206857434</v>
+        <v>0.2339922411376314</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.04562139685318201</v>
+        <v>0.04509701298130642</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3627937522746653</v>
+        <v>0.3646937522746653</v>
       </c>
       <c r="C89">
-        <v>-9.790319411526333</v>
+        <v>-10.12668628630198</v>
       </c>
       <c r="D89">
-        <v>12.55214058847367</v>
+        <v>12.47735371369803</v>
       </c>
       <c r="E89">
-        <v>22.69946</v>
+        <v>22.96104</v>
       </c>
       <c r="F89">
-        <v>22.75746</v>
+        <v>23.01904</v>
       </c>
       <c r="G89">
         <v>0.415</v>
@@ -8713,37 +8713,37 @@
         <v>0.242</v>
       </c>
       <c r="M89">
-        <v>5.366209068000001</v>
+        <v>5.427889632</v>
       </c>
       <c r="N89">
-        <v>-5.124209068000001</v>
+        <v>-5.185889632</v>
       </c>
       <c r="O89">
-        <v>-0.8711155415600002</v>
+        <v>-0.8816012374400001</v>
       </c>
       <c r="P89">
-        <v>-4.253093526440001</v>
+        <v>-4.30428839456</v>
       </c>
       <c r="Q89">
-        <v>-4.136093526440001</v>
+        <v>-4.18728839456</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.224773096037892</v>
+        <v>1.32302085404105</v>
       </c>
       <c r="T89">
-        <v>4.222279786596976</v>
+        <v>4.574136435480058</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.007666492206822083</v>
+        <v>0.007579372977199106</v>
       </c>
       <c r="W89">
-        <v>0.2339922411376314</v>
+        <v>0.2340127838519765</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.04509701298130642</v>
+        <v>0.0445845469247006</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3646937522746653</v>
+        <v>0.3665937522746653</v>
       </c>
       <c r="C90">
-        <v>-10.12668628630198</v>
+        <v>-10.46216726438501</v>
       </c>
       <c r="D90">
-        <v>12.47735371369803</v>
+        <v>12.40345273561499</v>
       </c>
       <c r="E90">
-        <v>22.96104</v>
+        <v>23.22262</v>
       </c>
       <c r="F90">
-        <v>23.01904</v>
+        <v>23.28062</v>
       </c>
       <c r="G90">
         <v>0.415</v>
@@ -8795,37 +8795,37 @@
         <v>0.242</v>
       </c>
       <c r="M90">
-        <v>5.427889632</v>
+        <v>5.489570196000001</v>
       </c>
       <c r="N90">
-        <v>-5.185889632</v>
+        <v>-5.247570196000001</v>
       </c>
       <c r="O90">
-        <v>-0.8816012374400001</v>
+        <v>-0.8920869333200002</v>
       </c>
       <c r="P90">
-        <v>-4.30428839456</v>
+        <v>-4.355483262680001</v>
       </c>
       <c r="Q90">
-        <v>-4.18728839456</v>
+        <v>-4.238483262680001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.32302085404105</v>
+        <v>1.439131840772055</v>
       </c>
       <c r="T90">
-        <v>4.574136435480058</v>
+        <v>4.9899670205237</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.007579372977199106</v>
+        <v>0.007494211483073272</v>
       </c>
       <c r="W90">
-        <v>0.2340127838519765</v>
+        <v>0.2340328649322913</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.0445845469247006</v>
+        <v>0.04408359695925457</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3665937522746653</v>
+        <v>0.3684937522746653</v>
       </c>
       <c r="C91">
-        <v>-10.46216726438501</v>
+        <v>-10.79677799408321</v>
       </c>
       <c r="D91">
-        <v>12.40345273561499</v>
+        <v>12.33042200591679</v>
       </c>
       <c r="E91">
-        <v>23.22262</v>
+        <v>23.4842</v>
       </c>
       <c r="F91">
-        <v>23.28062</v>
+        <v>23.5422</v>
       </c>
       <c r="G91">
         <v>0.415</v>
@@ -8877,37 +8877,37 @@
         <v>0.242</v>
       </c>
       <c r="M91">
-        <v>5.489570196000001</v>
+        <v>5.55125076</v>
       </c>
       <c r="N91">
-        <v>-5.247570196000001</v>
+        <v>-5.30925076</v>
       </c>
       <c r="O91">
-        <v>-0.8920869333200002</v>
+        <v>-0.9025726292000001</v>
       </c>
       <c r="P91">
-        <v>-4.355483262680001</v>
+        <v>-4.4066781308</v>
       </c>
       <c r="Q91">
-        <v>-4.238483262680001</v>
+        <v>-4.2896781308</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.439131840772055</v>
+        <v>1.57846502484926</v>
       </c>
       <c r="T91">
-        <v>4.9899670205237</v>
+        <v>5.48896372257607</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.007494211483073272</v>
+        <v>0.007410942466594682</v>
       </c>
       <c r="W91">
-        <v>0.2340328649322913</v>
+        <v>0.234052499766377</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.04408359695925457</v>
+        <v>0.04359377921526286</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3684937522746653</v>
+        <v>0.3703937522746653</v>
       </c>
       <c r="C92">
-        <v>-10.79677799408321</v>
+        <v>-11.13053375731669</v>
       </c>
       <c r="D92">
-        <v>12.33042200591679</v>
+        <v>12.25824624268331</v>
       </c>
       <c r="E92">
-        <v>23.4842</v>
+        <v>23.74578</v>
       </c>
       <c r="F92">
-        <v>23.5422</v>
+        <v>23.80378</v>
       </c>
       <c r="G92">
         <v>0.415</v>
@@ -8959,37 +8959,37 @@
         <v>0.242</v>
       </c>
       <c r="M92">
-        <v>5.55125076</v>
+        <v>5.612931324000001</v>
       </c>
       <c r="N92">
-        <v>-5.30925076</v>
+        <v>-5.370931324000001</v>
       </c>
       <c r="O92">
-        <v>-0.9025726292000001</v>
+        <v>-0.9130583250800002</v>
       </c>
       <c r="P92">
-        <v>-4.4066781308</v>
+        <v>-4.457872998920001</v>
       </c>
       <c r="Q92">
-        <v>-4.2896781308</v>
+        <v>-4.340872998920001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.57846502484926</v>
+        <v>1.748761138721401</v>
       </c>
       <c r="T92">
-        <v>5.48896372257607</v>
+        <v>6.098848580640079</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.007410942466594682</v>
+        <v>0.007329503538390343</v>
       </c>
       <c r="W92">
-        <v>0.234052499766377</v>
+        <v>0.2340717030656476</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.04359377921526286</v>
+        <v>0.04311472669641381</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3703937522746653</v>
+        <v>0.3722937522746653</v>
       </c>
       <c r="C93">
-        <v>-11.13053375731669</v>
+        <v>-11.46344948027872</v>
       </c>
       <c r="D93">
-        <v>12.25824624268331</v>
+        <v>12.18691051972128</v>
       </c>
       <c r="E93">
-        <v>23.74578</v>
+        <v>24.00736</v>
       </c>
       <c r="F93">
-        <v>23.80378</v>
+        <v>24.06536</v>
       </c>
       <c r="G93">
         <v>0.415</v>
@@ -9041,37 +9041,37 @@
         <v>0.242</v>
       </c>
       <c r="M93">
-        <v>5.612931324000001</v>
+        <v>5.674611888</v>
       </c>
       <c r="N93">
-        <v>-5.370931324000001</v>
+        <v>-5.432611888</v>
       </c>
       <c r="O93">
-        <v>-0.9130583250800002</v>
+        <v>-0.9235440209600001</v>
       </c>
       <c r="P93">
-        <v>-4.457872998920001</v>
+        <v>-4.509067867040001</v>
       </c>
       <c r="Q93">
-        <v>-4.340872998920001</v>
+        <v>-4.392067867040001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.748761138721401</v>
+        <v>1.961631281061577</v>
       </c>
       <c r="T93">
-        <v>6.098848580640079</v>
+        <v>6.861204653220091</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.007329503538390343</v>
+        <v>0.00724983502166871</v>
       </c>
       <c r="W93">
-        <v>0.2340717030656476</v>
+        <v>0.2340904889018905</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.04311472669641381</v>
+        <v>0.04264608836275707</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3722937522746653</v>
+        <v>0.3741937522746653</v>
       </c>
       <c r="C94">
-        <v>-11.46344948027872</v>
+        <v>-11.79553974372643</v>
       </c>
       <c r="D94">
-        <v>12.18691051972128</v>
+        <v>12.11640025627357</v>
       </c>
       <c r="E94">
-        <v>24.00736</v>
+        <v>24.26894</v>
       </c>
       <c r="F94">
-        <v>24.06536</v>
+        <v>24.32694</v>
       </c>
       <c r="G94">
         <v>0.415</v>
@@ -9123,37 +9123,37 @@
         <v>0.242</v>
       </c>
       <c r="M94">
-        <v>5.674611888</v>
+        <v>5.736292452000002</v>
       </c>
       <c r="N94">
-        <v>-5.432611888</v>
+        <v>-5.494292452000002</v>
       </c>
       <c r="O94">
-        <v>-0.9235440209600001</v>
+        <v>-0.9340297168400004</v>
       </c>
       <c r="P94">
-        <v>-4.509067867040001</v>
+        <v>-4.560262735160001</v>
       </c>
       <c r="Q94">
-        <v>-4.392067867040001</v>
+        <v>-4.443262735160001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.961631281061577</v>
+        <v>2.235321464070373</v>
       </c>
       <c r="T94">
-        <v>6.861204653220091</v>
+        <v>7.841376746537248</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.00724983502166871</v>
+        <v>0.007171879806381948</v>
       </c>
       <c r="W94">
-        <v>0.2340904889018905</v>
+        <v>0.2341088707416552</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.04264608836275707</v>
+        <v>0.04218752827283501</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3741937522746653</v>
+        <v>0.3760937522746653</v>
       </c>
       <c r="C95">
-        <v>-11.79553974372643</v>
+        <v>-12.12681879291637</v>
       </c>
       <c r="D95">
-        <v>12.11640025627357</v>
+        <v>12.04670120708363</v>
       </c>
       <c r="E95">
-        <v>24.26894</v>
+        <v>24.53052</v>
       </c>
       <c r="F95">
-        <v>24.32694</v>
+        <v>24.58852</v>
       </c>
       <c r="G95">
         <v>0.415</v>
@@ -9205,37 +9205,37 @@
         <v>0.242</v>
       </c>
       <c r="M95">
-        <v>5.736292452000002</v>
+        <v>5.797973016000001</v>
       </c>
       <c r="N95">
-        <v>-5.494292452000002</v>
+        <v>-5.555973016000001</v>
       </c>
       <c r="O95">
-        <v>-0.9340297168400004</v>
+        <v>-0.9445154127200003</v>
       </c>
       <c r="P95">
-        <v>-4.560262735160001</v>
+        <v>-4.611457603280001</v>
       </c>
       <c r="Q95">
-        <v>-4.443262735160001</v>
+        <v>-4.494457603280001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.235321464070373</v>
+        <v>2.600241708082103</v>
       </c>
       <c r="T95">
-        <v>7.841376746537248</v>
+        <v>9.148272870960126</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.007171879806381948</v>
+        <v>0.007095583212697034</v>
       </c>
       <c r="W95">
-        <v>0.2341088707416552</v>
+        <v>0.2341268614784461</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.04218752827283501</v>
+        <v>0.04173872478057084</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3760937522746653</v>
+        <v>0.3779937522746653</v>
       </c>
       <c r="C96">
-        <v>-12.12681879291637</v>
+        <v>-12.45730054719901</v>
       </c>
       <c r="D96">
-        <v>12.04670120708363</v>
+        <v>11.97779945280099</v>
       </c>
       <c r="E96">
-        <v>24.53052</v>
+        <v>24.7921</v>
       </c>
       <c r="F96">
-        <v>24.58852</v>
+        <v>24.8501</v>
       </c>
       <c r="G96">
         <v>0.415</v>
@@ -9287,37 +9287,37 @@
         <v>0.242</v>
       </c>
       <c r="M96">
-        <v>5.797973016000001</v>
+        <v>5.859653580000001</v>
       </c>
       <c r="N96">
-        <v>-5.555973016000001</v>
+        <v>-5.617653580000001</v>
       </c>
       <c r="O96">
-        <v>-0.9445154127200003</v>
+        <v>-0.9550011086000002</v>
       </c>
       <c r="P96">
-        <v>-4.611457603280001</v>
+        <v>-4.6626524714</v>
       </c>
       <c r="Q96">
-        <v>-4.494457603280001</v>
+        <v>-4.5456524714</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.600241708082103</v>
+        <v>3.111130049698525</v>
       </c>
       <c r="T96">
-        <v>9.148272870960126</v>
+        <v>10.97792744515215</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.007095583212697034</v>
+        <v>0.007020892863089697</v>
       </c>
       <c r="W96">
-        <v>0.2341268614784461</v>
+        <v>0.2341444734628834</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.04173872478057084</v>
+        <v>0.04129936978288062</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3779937522746653</v>
+        <v>0.3798937522746654</v>
       </c>
       <c r="C97">
-        <v>-12.45730054719901</v>
+        <v>-12.78699860928601</v>
       </c>
       <c r="D97">
-        <v>11.97779945280099</v>
+        <v>11.909681390714</v>
       </c>
       <c r="E97">
-        <v>24.7921</v>
+        <v>25.05368</v>
       </c>
       <c r="F97">
-        <v>24.8501</v>
+        <v>25.11168</v>
       </c>
       <c r="G97">
         <v>0.415</v>
@@ -9369,37 +9369,37 @@
         <v>0.242</v>
       </c>
       <c r="M97">
-        <v>5.859653580000001</v>
+        <v>5.921334144000001</v>
       </c>
       <c r="N97">
-        <v>-5.617653580000001</v>
+        <v>-5.679334144000001</v>
       </c>
       <c r="O97">
-        <v>-0.9550011086000002</v>
+        <v>-0.9654868044800002</v>
       </c>
       <c r="P97">
-        <v>-4.6626524714</v>
+        <v>-4.713847339520001</v>
       </c>
       <c r="Q97">
-        <v>-4.5456524714</v>
+        <v>-4.596847339520001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.111130049698525</v>
+        <v>3.877462562123158</v>
       </c>
       <c r="T97">
-        <v>10.97792744515215</v>
+        <v>13.7224093064402</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.007020892863089697</v>
+        <v>0.006947758562432513</v>
       </c>
       <c r="W97">
-        <v>0.2341444734628834</v>
+        <v>0.2341617185309784</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.04129936978288062</v>
+        <v>0.04086916801430884</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3798937522746654</v>
+        <v>0.3817937522746653</v>
       </c>
       <c r="C98">
-        <v>-12.78699860928601</v>
+        <v>-13.11592627420288</v>
       </c>
       <c r="D98">
-        <v>11.909681390714</v>
+        <v>11.84233372579713</v>
       </c>
       <c r="E98">
-        <v>25.05368</v>
+        <v>25.31526</v>
       </c>
       <c r="F98">
-        <v>25.11168</v>
+        <v>25.37326</v>
       </c>
       <c r="G98">
         <v>0.415</v>
@@ -9451,37 +9451,37 @@
         <v>0.242</v>
       </c>
       <c r="M98">
-        <v>5.921334144</v>
+        <v>5.983014708000001</v>
       </c>
       <c r="N98">
-        <v>-5.679334144</v>
+        <v>-5.741014708000001</v>
       </c>
       <c r="O98">
-        <v>-0.9654868044800001</v>
+        <v>-0.9759725003600002</v>
       </c>
       <c r="P98">
-        <v>-4.71384733952</v>
+        <v>-4.765042207640001</v>
       </c>
       <c r="Q98">
-        <v>-4.59684733952</v>
+        <v>-4.648042207640001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.877462562123148</v>
+        <v>5.154683416164197</v>
       </c>
       <c r="T98">
-        <v>13.72240930644016</v>
+        <v>18.29654574192022</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.006947758562432515</v>
+        <v>0.006876132185500219</v>
       </c>
       <c r="W98">
-        <v>0.2341617185309784</v>
+        <v>0.2341786080306591</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04086916801430895</v>
+        <v>0.04044783638529537</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3817937522746653</v>
+        <v>0.3836937522746653</v>
       </c>
       <c r="C99">
-        <v>-13.11592627420288</v>
+        <v>-13.44409653793976</v>
       </c>
       <c r="D99">
-        <v>11.84233372579713</v>
+        <v>11.77574346206024</v>
       </c>
       <c r="E99">
-        <v>25.31526</v>
+        <v>25.57684</v>
       </c>
       <c r="F99">
-        <v>25.37326</v>
+        <v>25.63484</v>
       </c>
       <c r="G99">
         <v>0.415</v>
@@ -9533,37 +9533,37 @@
         <v>0.242</v>
       </c>
       <c r="M99">
-        <v>5.983014708000001</v>
+        <v>6.044695272</v>
       </c>
       <c r="N99">
-        <v>-5.741014708000001</v>
+        <v>-5.802695272</v>
       </c>
       <c r="O99">
-        <v>-0.9759725003600002</v>
+        <v>-0.9864581962400001</v>
       </c>
       <c r="P99">
-        <v>-4.765042207640001</v>
+        <v>-4.81623707576</v>
       </c>
       <c r="Q99">
-        <v>-4.648042207640001</v>
+        <v>-4.69923707576</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.154683416164197</v>
+        <v>7.709125124246295</v>
       </c>
       <c r="T99">
-        <v>18.29654574192022</v>
+        <v>27.44481861288033</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.006876132185500219</v>
+        <v>0.006805967571362462</v>
       </c>
       <c r="W99">
-        <v>0.2341786080306591</v>
+        <v>0.2341951528466727</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.04044783638529537</v>
+        <v>0.04003510336095562</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3836937522746653</v>
+        <v>0.3855937522746653</v>
       </c>
       <c r="C100">
-        <v>-13.44409653793976</v>
+        <v>-13.77152210581185</v>
       </c>
       <c r="D100">
-        <v>11.77574346206024</v>
+        <v>11.70989789418815</v>
       </c>
       <c r="E100">
-        <v>25.57684</v>
+        <v>25.83842</v>
       </c>
       <c r="F100">
-        <v>25.63484</v>
+        <v>25.89642</v>
       </c>
       <c r="G100">
         <v>0.415</v>
@@ -9615,37 +9615,37 @@
         <v>0.242</v>
       </c>
       <c r="M100">
-        <v>6.044695272</v>
+        <v>6.106375836000001</v>
       </c>
       <c r="N100">
-        <v>-5.802695272</v>
+        <v>-5.864375836000001</v>
       </c>
       <c r="O100">
-        <v>-0.9864581962400001</v>
+        <v>-0.9969438921200002</v>
       </c>
       <c r="P100">
-        <v>-4.81623707576</v>
+        <v>-4.867431943880001</v>
       </c>
       <c r="Q100">
-        <v>-4.69923707576</v>
+        <v>-4.750431943880001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.709125124246295</v>
+        <v>15.37245024849259</v>
       </c>
       <c r="T100">
-        <v>27.44481861288033</v>
+        <v>54.88963722576065</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.006805967571362462</v>
+        <v>0.006737220424176983</v>
       </c>
       <c r="W100">
-        <v>0.2341951528466727</v>
+        <v>0.2342113634239791</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04003510336095562</v>
+        <v>0.0396307083775117</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3855937522746653</v>
-      </c>
-      <c r="C101">
-        <v>-13.77152210581185</v>
-      </c>
-      <c r="D101">
-        <v>11.70989789418815</v>
-      </c>
-      <c r="E101">
-        <v>25.83842</v>
-      </c>
-      <c r="F101">
-        <v>25.89642</v>
-      </c>
-      <c r="G101">
-        <v>0.415</v>
-      </c>
-      <c r="H101">
-        <v>26.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.359</v>
-      </c>
-      <c r="K101">
-        <v>0.117</v>
-      </c>
-      <c r="L101">
-        <v>0.242</v>
-      </c>
-      <c r="M101">
-        <v>6.106375836000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.864375836000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.9969438921200002</v>
-      </c>
-      <c r="P101">
-        <v>-4.867431943880001</v>
-      </c>
-      <c r="Q101">
-        <v>-4.750431943880001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>15.37245024849259</v>
-      </c>
-      <c r="T101">
-        <v>54.88963722576065</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.006737220424176983</v>
-      </c>
-      <c r="W101">
-        <v>0.2342113634239791</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.0396307083775117</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
